--- a/TWS API/source/pythonclient/Trading Strategies/Trade Journal/Live Test Journal/ZTH Trade Tracker - AB.xlsx
+++ b/TWS API/source/pythonclient/Trading Strategies/Trade Journal/Live Test Journal/ZTH Trade Tracker - AB.xlsx
@@ -1,19 +1,19 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Trade Tracker - Eval" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Multipliers" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Tag Options" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Trading Rules" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Analysis" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="AI Suggestions" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Economic News" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Indicators" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="Trade Tracker - Eval" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Multipliers" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Tag Options" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Trading Rules" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Indicators" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="Economic News" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="Analysis" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="AI Suggestions" sheetId="8" state="visible" r:id="rId8"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="191029" fullCalcOnLoad="1"/>
@@ -5833,25 +5833,79 @@
       <c r="AA62" s="5" t="n"/>
     </row>
     <row r="63" ht="15.75" customHeight="1">
-      <c r="A63" s="5" t="n"/>
-      <c r="B63" s="13" t="n"/>
-      <c r="C63" s="10" t="n"/>
-      <c r="D63" s="5" t="n"/>
-      <c r="E63" s="5" t="n"/>
-      <c r="F63" s="5" t="n"/>
-      <c r="G63" s="5" t="n"/>
-      <c r="H63" s="5" t="n"/>
-      <c r="I63" s="5" t="n"/>
-      <c r="J63" s="5" t="n"/>
-      <c r="K63" s="8" t="n"/>
-      <c r="L63" s="8" t="n"/>
-      <c r="M63" s="5" t="n"/>
-      <c r="N63" s="16" t="n"/>
-      <c r="O63" s="9" t="n"/>
-      <c r="P63" s="5" t="n"/>
-      <c r="Q63" s="5" t="n"/>
-      <c r="R63" s="5" t="n"/>
-      <c r="S63" s="5" t="n"/>
+      <c r="A63" s="5" t="n">
+        <v>62</v>
+      </c>
+      <c r="B63" s="23" t="n">
+        <v>46299</v>
+      </c>
+      <c r="C63" s="10" t="n">
+        <v>0.8978472222222222</v>
+      </c>
+      <c r="D63" s="5" t="inlineStr">
+        <is>
+          <t>MGC</t>
+        </is>
+      </c>
+      <c r="E63" s="5" t="inlineStr">
+        <is>
+          <t>Short</t>
+        </is>
+      </c>
+      <c r="F63" s="5" t="n">
+        <v>4184.833333</v>
+      </c>
+      <c r="G63" s="5" t="n">
+        <v>4188.066667</v>
+      </c>
+      <c r="H63" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="I63" s="5" t="n">
+        <v>4191.4</v>
+      </c>
+      <c r="J63" s="5" t="n">
+        <v>4176.4</v>
+      </c>
+      <c r="K63" s="8">
+        <f>IF(AND(I63&lt;&gt;"",J63&lt;&gt;"",F63&lt;&gt;""), (J63-F63)/(F63-I63), "")</f>
+        <v/>
+      </c>
+      <c r="L63" s="8">
+        <f>IF(AND(F63&lt;&gt;"",G63&lt;&gt;"",I63&lt;&gt;""), (G63-F63)/(F63-I63), "")</f>
+        <v/>
+      </c>
+      <c r="M63" s="5">
+        <f>IF(N63&gt;0,"Win",IF(N63&lt;0,"Loss",""))</f>
+        <v/>
+      </c>
+      <c r="N63" s="16">
+        <f>IF(AND(F63&lt;&gt;"",G63&lt;&gt;"",H63&lt;&gt;"",D63&lt;&gt;""), IF(E63="Long", (G63-F63)*H63*VLOOKUP(D63,Multipliers!A:B,2,FALSE), (F63-G63)*H63*VLOOKUP(D63,Multipliers!A:B,2,FALSE)), "")</f>
+        <v/>
+      </c>
+      <c r="O63" s="9">
+        <f>IF(AND(N63&lt;&gt;"",F63&lt;&gt;"",H63&lt;&gt;"",D63&lt;&gt;""), N63/(F63*H63*VLOOKUP(D63,Multipliers!A:B,2,FALSE)), "")</f>
+        <v/>
+      </c>
+      <c r="P63" s="5">
+        <f>P62+N63</f>
+        <v/>
+      </c>
+      <c r="Q63" s="5" t="inlineStr">
+        <is>
+          <t>Break and Retest</t>
+        </is>
+      </c>
+      <c r="R63" s="5" t="inlineStr">
+        <is>
+          <t>Imported from Tradovate</t>
+        </is>
+      </c>
+      <c r="S63" s="5" t="inlineStr">
+        <is>
+          <t>MGC</t>
+        </is>
+      </c>
       <c r="T63" s="5" t="n"/>
       <c r="U63" s="5" t="n"/>
       <c r="V63" s="5" t="n"/>
@@ -5862,25 +5916,79 @@
       <c r="AA63" s="5" t="n"/>
     </row>
     <row r="64" ht="15.75" customHeight="1">
-      <c r="A64" s="5" t="n"/>
-      <c r="B64" s="13" t="n"/>
-      <c r="C64" s="10" t="n"/>
-      <c r="D64" s="5" t="n"/>
-      <c r="E64" s="5" t="n"/>
-      <c r="F64" s="5" t="n"/>
-      <c r="G64" s="5" t="n"/>
-      <c r="H64" s="5" t="n"/>
-      <c r="I64" s="5" t="n"/>
-      <c r="J64" s="5" t="n"/>
-      <c r="K64" s="8" t="n"/>
-      <c r="L64" s="8" t="n"/>
-      <c r="M64" s="5" t="n"/>
-      <c r="N64" s="16" t="n"/>
-      <c r="O64" s="9" t="n"/>
-      <c r="P64" s="5" t="n"/>
-      <c r="Q64" s="5" t="n"/>
-      <c r="R64" s="5" t="n"/>
-      <c r="S64" s="5" t="n"/>
+      <c r="A64" s="5" t="n">
+        <v>63</v>
+      </c>
+      <c r="B64" s="23" t="n">
+        <v>46299</v>
+      </c>
+      <c r="C64" s="10" t="n">
+        <v>0.9133101851851851</v>
+      </c>
+      <c r="D64" s="5" t="inlineStr">
+        <is>
+          <t>MGC</t>
+        </is>
+      </c>
+      <c r="E64" s="5" t="inlineStr">
+        <is>
+          <t>Short</t>
+        </is>
+      </c>
+      <c r="F64" s="5" t="n">
+        <v>4187.2</v>
+      </c>
+      <c r="G64" s="5" t="n">
+        <v>4189.1</v>
+      </c>
+      <c r="H64" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="I64" s="5" t="n">
+        <v>4191.4</v>
+      </c>
+      <c r="J64" s="5" t="n">
+        <v>4185.4</v>
+      </c>
+      <c r="K64" s="8">
+        <f>IF(AND(I64&lt;&gt;"",J64&lt;&gt;"",F64&lt;&gt;""), (J64-F64)/(F64-I64), "")</f>
+        <v/>
+      </c>
+      <c r="L64" s="8">
+        <f>IF(AND(F64&lt;&gt;"",G64&lt;&gt;"",I64&lt;&gt;""), (G64-F64)/(F64-I64), "")</f>
+        <v/>
+      </c>
+      <c r="M64" s="5">
+        <f>IF(N64&gt;0,"Win",IF(N64&lt;0,"Loss",""))</f>
+        <v/>
+      </c>
+      <c r="N64" s="16">
+        <f>IF(AND(F64&lt;&gt;"",G64&lt;&gt;"",H64&lt;&gt;"",D64&lt;&gt;""), IF(E64="Long", (G64-F64)*H64*VLOOKUP(D64,Multipliers!A:B,2,FALSE), (F64-G64)*H64*VLOOKUP(D64,Multipliers!A:B,2,FALSE)), "")</f>
+        <v/>
+      </c>
+      <c r="O64" s="9">
+        <f>IF(AND(N64&lt;&gt;"",F64&lt;&gt;"",H64&lt;&gt;"",D64&lt;&gt;""), N64/(F64*H64*VLOOKUP(D64,Multipliers!A:B,2,FALSE)), "")</f>
+        <v/>
+      </c>
+      <c r="P64" s="5">
+        <f>P63+N64</f>
+        <v/>
+      </c>
+      <c r="Q64" s="5" t="inlineStr">
+        <is>
+          <t>Break and Retest</t>
+        </is>
+      </c>
+      <c r="R64" s="5" t="inlineStr">
+        <is>
+          <t>Imported from Tradovate</t>
+        </is>
+      </c>
+      <c r="S64" s="5" t="inlineStr">
+        <is>
+          <t>MGC</t>
+        </is>
+      </c>
       <c r="T64" s="5" t="n"/>
       <c r="U64" s="5" t="n"/>
       <c r="V64" s="5" t="n"/>
@@ -5891,28 +5999,84 @@
       <c r="AA64" s="5" t="n"/>
     </row>
     <row r="65" ht="15.75" customHeight="1">
-      <c r="A65" s="5" t="n"/>
-      <c r="B65" s="13" t="n"/>
-      <c r="C65" s="10" t="n"/>
-      <c r="D65" s="5" t="n"/>
-      <c r="E65" s="5" t="n"/>
-      <c r="F65" s="5" t="n"/>
-      <c r="G65" s="5" t="n"/>
-      <c r="H65" s="5" t="n"/>
+      <c r="A65" s="5" t="n">
+        <v>64</v>
+      </c>
+      <c r="B65" s="23" t="n">
+        <v>46299</v>
+      </c>
+      <c r="C65" s="10" t="n">
+        <v>0.9154282407407407</v>
+      </c>
+      <c r="D65" s="5" t="inlineStr">
+        <is>
+          <t>MGC</t>
+        </is>
+      </c>
+      <c r="E65" s="5" t="inlineStr">
+        <is>
+          <t>Long</t>
+        </is>
+      </c>
+      <c r="F65" s="5" t="n">
+        <v>4189.1</v>
+      </c>
+      <c r="G65" s="5" t="n">
+        <v>4189.7</v>
+      </c>
+      <c r="H65" s="5" t="n">
+        <v>3</v>
+      </c>
       <c r="I65" s="5" t="n"/>
-      <c r="J65" s="5" t="n"/>
-      <c r="K65" s="8" t="n"/>
-      <c r="L65" s="8" t="n"/>
-      <c r="M65" s="5" t="n"/>
-      <c r="N65" s="16" t="n"/>
-      <c r="O65" s="9" t="n"/>
-      <c r="P65" s="5" t="n"/>
-      <c r="Q65" s="5" t="n"/>
-      <c r="R65" s="5" t="n"/>
-      <c r="S65" s="5" t="n"/>
+      <c r="J65" s="5" t="n">
+        <v>4189.7</v>
+      </c>
+      <c r="K65" s="8">
+        <f>IF(AND(I65&lt;&gt;"",J65&lt;&gt;"",F65&lt;&gt;""), (J65-F65)/(F65-I65), "")</f>
+        <v/>
+      </c>
+      <c r="L65" s="8">
+        <f>IF(AND(F65&lt;&gt;"",G65&lt;&gt;"",I65&lt;&gt;""), (G65-F65)/(F65-I65), "")</f>
+        <v/>
+      </c>
+      <c r="M65" s="5">
+        <f>IF(N65&gt;0,"Win",IF(N65&lt;0,"Loss",""))</f>
+        <v/>
+      </c>
+      <c r="N65" s="16">
+        <f>IF(AND(F65&lt;&gt;"",G65&lt;&gt;"",H65&lt;&gt;"",D65&lt;&gt;""), IF(E65="Long", (G65-F65)*H65*VLOOKUP(D65,Multipliers!A:B,2,FALSE), (F65-G65)*H65*VLOOKUP(D65,Multipliers!A:B,2,FALSE)), "")</f>
+        <v/>
+      </c>
+      <c r="O65" s="9">
+        <f>IF(AND(N65&lt;&gt;"",F65&lt;&gt;"",H65&lt;&gt;"",D65&lt;&gt;""), N65/(F65*H65*VLOOKUP(D65,Multipliers!A:B,2,FALSE)), "")</f>
+        <v/>
+      </c>
+      <c r="P65" s="5">
+        <f>P64+N65</f>
+        <v/>
+      </c>
+      <c r="Q65" s="5" t="inlineStr">
+        <is>
+          <t>Break and Retest</t>
+        </is>
+      </c>
+      <c r="R65" s="5" t="inlineStr">
+        <is>
+          <t>Imported from Tradovate</t>
+        </is>
+      </c>
+      <c r="S65" s="5" t="inlineStr">
+        <is>
+          <t>MGC</t>
+        </is>
+      </c>
       <c r="T65" s="5" t="n"/>
       <c r="U65" s="5" t="n"/>
-      <c r="V65" s="5" t="n"/>
+      <c r="V65" s="5" t="inlineStr">
+        <is>
+          <t>Revenge trade</t>
+        </is>
+      </c>
       <c r="W65" s="5" t="n"/>
       <c r="X65" s="5" t="n"/>
       <c r="Y65" s="5" t="n"/>
@@ -5920,25 +6084,77 @@
       <c r="AA65" s="5" t="n"/>
     </row>
     <row r="66" ht="15.75" customHeight="1">
-      <c r="A66" s="5" t="n"/>
-      <c r="B66" s="13" t="n"/>
-      <c r="C66" s="10" t="n"/>
-      <c r="D66" s="5" t="n"/>
-      <c r="E66" s="5" t="n"/>
-      <c r="F66" s="5" t="n"/>
-      <c r="G66" s="5" t="n"/>
-      <c r="H66" s="5" t="n"/>
+      <c r="A66" s="5" t="n">
+        <v>65</v>
+      </c>
+      <c r="B66" s="23" t="n">
+        <v>46299</v>
+      </c>
+      <c r="C66" s="10" t="n">
+        <v>0.9392592592592592</v>
+      </c>
+      <c r="D66" s="5" t="inlineStr">
+        <is>
+          <t>MGC</t>
+        </is>
+      </c>
+      <c r="E66" s="5" t="inlineStr">
+        <is>
+          <t>Long</t>
+        </is>
+      </c>
+      <c r="F66" s="5" t="n">
+        <v>4184.4</v>
+      </c>
+      <c r="G66" s="5" t="n">
+        <v>4169.5</v>
+      </c>
+      <c r="H66" s="5" t="n">
+        <v>3</v>
+      </c>
       <c r="I66" s="5" t="n"/>
-      <c r="J66" s="5" t="n"/>
-      <c r="K66" s="8" t="n"/>
-      <c r="L66" s="8" t="n"/>
-      <c r="M66" s="5" t="n"/>
-      <c r="N66" s="16" t="n"/>
-      <c r="O66" s="9" t="n"/>
-      <c r="P66" s="5" t="n"/>
-      <c r="Q66" s="5" t="n"/>
-      <c r="R66" s="5" t="n"/>
-      <c r="S66" s="5" t="n"/>
+      <c r="J66" s="5" t="n">
+        <v>4185.1</v>
+      </c>
+      <c r="K66" s="8">
+        <f>IF(AND(I66&lt;&gt;"",J66&lt;&gt;"",F66&lt;&gt;""), (J66-F66)/(F66-I66), "")</f>
+        <v/>
+      </c>
+      <c r="L66" s="8">
+        <f>IF(AND(F66&lt;&gt;"",G66&lt;&gt;"",I66&lt;&gt;""), (G66-F66)/(F66-I66), "")</f>
+        <v/>
+      </c>
+      <c r="M66" s="5">
+        <f>IF(N66&gt;0,"Win",IF(N66&lt;0,"Loss",""))</f>
+        <v/>
+      </c>
+      <c r="N66" s="16">
+        <f>IF(AND(F66&lt;&gt;"",G66&lt;&gt;"",H66&lt;&gt;"",D66&lt;&gt;""), IF(E66="Long", (G66-F66)*H66*VLOOKUP(D66,Multipliers!A:B,2,FALSE), (F66-G66)*H66*VLOOKUP(D66,Multipliers!A:B,2,FALSE)), "")</f>
+        <v/>
+      </c>
+      <c r="O66" s="9">
+        <f>IF(AND(N66&lt;&gt;"",F66&lt;&gt;"",H66&lt;&gt;"",D66&lt;&gt;""), N66/(F66*H66*VLOOKUP(D66,Multipliers!A:B,2,FALSE)), "")</f>
+        <v/>
+      </c>
+      <c r="P66" s="5">
+        <f>P65+N66</f>
+        <v/>
+      </c>
+      <c r="Q66" s="5" t="inlineStr">
+        <is>
+          <t>Break and Retest</t>
+        </is>
+      </c>
+      <c r="R66" s="5" t="inlineStr">
+        <is>
+          <t>Imported from Tradovate</t>
+        </is>
+      </c>
+      <c r="S66" s="5" t="inlineStr">
+        <is>
+          <t>MGC</t>
+        </is>
+      </c>
       <c r="T66" s="5" t="n"/>
       <c r="U66" s="5" t="n"/>
       <c r="V66" s="5" t="n"/>
@@ -5949,25 +6165,77 @@
       <c r="AA66" s="5" t="n"/>
     </row>
     <row r="67" ht="15.75" customHeight="1">
-      <c r="A67" s="5" t="n"/>
-      <c r="B67" s="13" t="n"/>
-      <c r="C67" s="10" t="n"/>
-      <c r="D67" s="5" t="n"/>
-      <c r="E67" s="5" t="n"/>
-      <c r="F67" s="5" t="n"/>
-      <c r="G67" s="5" t="n"/>
-      <c r="H67" s="5" t="n"/>
+      <c r="A67" s="5" t="n">
+        <v>66</v>
+      </c>
+      <c r="B67" s="23" t="n">
+        <v>46299</v>
+      </c>
+      <c r="C67" s="10" t="n">
+        <v>0.9571064814814815</v>
+      </c>
+      <c r="D67" s="5" t="inlineStr">
+        <is>
+          <t>MGC</t>
+        </is>
+      </c>
+      <c r="E67" s="5" t="inlineStr">
+        <is>
+          <t>Long</t>
+        </is>
+      </c>
+      <c r="F67" s="5" t="n">
+        <v>4170.6</v>
+      </c>
+      <c r="G67" s="5" t="n">
+        <v>4171.3</v>
+      </c>
+      <c r="H67" s="5" t="n">
+        <v>1</v>
+      </c>
       <c r="I67" s="5" t="n"/>
-      <c r="J67" s="5" t="n"/>
-      <c r="K67" s="8" t="n"/>
-      <c r="L67" s="8" t="n"/>
-      <c r="M67" s="5" t="n"/>
-      <c r="N67" s="16" t="n"/>
-      <c r="O67" s="9" t="n"/>
-      <c r="P67" s="5" t="n"/>
-      <c r="Q67" s="5" t="n"/>
-      <c r="R67" s="5" t="n"/>
-      <c r="S67" s="5" t="n"/>
+      <c r="J67" s="5" t="n">
+        <v>4171.3</v>
+      </c>
+      <c r="K67" s="8">
+        <f>IF(AND(I67&lt;&gt;"",J67&lt;&gt;"",F67&lt;&gt;""), (J67-F67)/(F67-I67), "")</f>
+        <v/>
+      </c>
+      <c r="L67" s="8">
+        <f>IF(AND(F67&lt;&gt;"",G67&lt;&gt;"",I67&lt;&gt;""), (G67-F67)/(F67-I67), "")</f>
+        <v/>
+      </c>
+      <c r="M67" s="5">
+        <f>IF(N67&gt;0,"Win",IF(N67&lt;0,"Loss",""))</f>
+        <v/>
+      </c>
+      <c r="N67" s="16">
+        <f>IF(AND(F67&lt;&gt;"",G67&lt;&gt;"",H67&lt;&gt;"",D67&lt;&gt;""), IF(E67="Long", (G67-F67)*H67*VLOOKUP(D67,Multipliers!A:B,2,FALSE), (F67-G67)*H67*VLOOKUP(D67,Multipliers!A:B,2,FALSE)), "")</f>
+        <v/>
+      </c>
+      <c r="O67" s="9">
+        <f>IF(AND(N67&lt;&gt;"",F67&lt;&gt;"",H67&lt;&gt;"",D67&lt;&gt;""), N67/(F67*H67*VLOOKUP(D67,Multipliers!A:B,2,FALSE)), "")</f>
+        <v/>
+      </c>
+      <c r="P67" s="5">
+        <f>P66+N67</f>
+        <v/>
+      </c>
+      <c r="Q67" s="5" t="inlineStr">
+        <is>
+          <t>Break and Retest</t>
+        </is>
+      </c>
+      <c r="R67" s="5" t="inlineStr">
+        <is>
+          <t>Imported from Tradovate</t>
+        </is>
+      </c>
+      <c r="S67" s="5" t="inlineStr">
+        <is>
+          <t>MGC</t>
+        </is>
+      </c>
       <c r="T67" s="5" t="n"/>
       <c r="U67" s="5" t="n"/>
       <c r="V67" s="5" t="n"/>
@@ -5978,25 +6246,77 @@
       <c r="AA67" s="5" t="n"/>
     </row>
     <row r="68" ht="15.75" customHeight="1">
-      <c r="A68" s="5" t="n"/>
-      <c r="B68" s="13" t="n"/>
-      <c r="C68" s="10" t="n"/>
-      <c r="D68" s="5" t="n"/>
-      <c r="E68" s="5" t="n"/>
-      <c r="F68" s="5" t="n"/>
-      <c r="G68" s="5" t="n"/>
-      <c r="H68" s="5" t="n"/>
+      <c r="A68" s="5" t="n">
+        <v>67</v>
+      </c>
+      <c r="B68" s="23" t="n">
+        <v>46299</v>
+      </c>
+      <c r="C68" s="10" t="n">
+        <v>0.9605324074074074</v>
+      </c>
+      <c r="D68" s="5" t="inlineStr">
+        <is>
+          <t>MGC</t>
+        </is>
+      </c>
+      <c r="E68" s="5" t="inlineStr">
+        <is>
+          <t>Short</t>
+        </is>
+      </c>
+      <c r="F68" s="5" t="n">
+        <v>4167.366667</v>
+      </c>
+      <c r="G68" s="5" t="n">
+        <v>4167.2</v>
+      </c>
+      <c r="H68" s="5" t="n">
+        <v>3</v>
+      </c>
       <c r="I68" s="5" t="n"/>
-      <c r="J68" s="5" t="n"/>
-      <c r="K68" s="8" t="n"/>
-      <c r="L68" s="8" t="n"/>
-      <c r="M68" s="5" t="n"/>
-      <c r="N68" s="16" t="n"/>
-      <c r="O68" s="9" t="n"/>
-      <c r="P68" s="5" t="n"/>
-      <c r="Q68" s="5" t="n"/>
-      <c r="R68" s="5" t="n"/>
-      <c r="S68" s="5" t="n"/>
+      <c r="J68" s="5" t="n">
+        <v>4156.6</v>
+      </c>
+      <c r="K68" s="8">
+        <f>IF(AND(I68&lt;&gt;"",J68&lt;&gt;"",F68&lt;&gt;""), (J68-F68)/(F68-I68), "")</f>
+        <v/>
+      </c>
+      <c r="L68" s="8">
+        <f>IF(AND(F68&lt;&gt;"",G68&lt;&gt;"",I68&lt;&gt;""), (G68-F68)/(F68-I68), "")</f>
+        <v/>
+      </c>
+      <c r="M68" s="5">
+        <f>IF(N68&gt;0,"Win",IF(N68&lt;0,"Loss",""))</f>
+        <v/>
+      </c>
+      <c r="N68" s="16">
+        <f>IF(AND(F68&lt;&gt;"",G68&lt;&gt;"",H68&lt;&gt;"",D68&lt;&gt;""), IF(E68="Long", (G68-F68)*H68*VLOOKUP(D68,Multipliers!A:B,2,FALSE), (F68-G68)*H68*VLOOKUP(D68,Multipliers!A:B,2,FALSE)), "")</f>
+        <v/>
+      </c>
+      <c r="O68" s="9">
+        <f>IF(AND(N68&lt;&gt;"",F68&lt;&gt;"",H68&lt;&gt;"",D68&lt;&gt;""), N68/(F68*H68*VLOOKUP(D68,Multipliers!A:B,2,FALSE)), "")</f>
+        <v/>
+      </c>
+      <c r="P68" s="5">
+        <f>P67+N68</f>
+        <v/>
+      </c>
+      <c r="Q68" s="5" t="inlineStr">
+        <is>
+          <t>Break and Retest</t>
+        </is>
+      </c>
+      <c r="R68" s="5" t="inlineStr">
+        <is>
+          <t>Imported from Tradovate</t>
+        </is>
+      </c>
+      <c r="S68" s="5" t="inlineStr">
+        <is>
+          <t>MGC</t>
+        </is>
+      </c>
       <c r="T68" s="5" t="n"/>
       <c r="U68" s="5" t="n"/>
       <c r="V68" s="5" t="n"/>
@@ -6007,25 +6327,77 @@
       <c r="AA68" s="5" t="n"/>
     </row>
     <row r="69" ht="15.75" customHeight="1">
-      <c r="A69" s="5" t="n"/>
-      <c r="B69" s="13" t="n"/>
-      <c r="C69" s="10" t="n"/>
-      <c r="D69" s="5" t="n"/>
-      <c r="E69" s="5" t="n"/>
-      <c r="F69" s="5" t="n"/>
-      <c r="G69" s="5" t="n"/>
-      <c r="H69" s="5" t="n"/>
+      <c r="A69" s="5" t="n">
+        <v>68</v>
+      </c>
+      <c r="B69" s="23" t="n">
+        <v>46301</v>
+      </c>
+      <c r="C69" s="10" t="n">
+        <v>0.422962962962963</v>
+      </c>
+      <c r="D69" s="5" t="inlineStr">
+        <is>
+          <t>MNQ</t>
+        </is>
+      </c>
+      <c r="E69" s="5" t="inlineStr">
+        <is>
+          <t>Long</t>
+        </is>
+      </c>
+      <c r="F69" s="5" t="n">
+        <v>31561</v>
+      </c>
+      <c r="G69" s="5" t="n">
+        <v>31563.5</v>
+      </c>
+      <c r="H69" s="5" t="n">
+        <v>2</v>
+      </c>
       <c r="I69" s="5" t="n"/>
-      <c r="J69" s="5" t="n"/>
-      <c r="K69" s="8" t="n"/>
-      <c r="L69" s="8" t="n"/>
-      <c r="M69" s="5" t="n"/>
-      <c r="N69" s="16" t="n"/>
-      <c r="O69" s="9" t="n"/>
-      <c r="P69" s="5" t="n"/>
-      <c r="Q69" s="5" t="n"/>
-      <c r="R69" s="5" t="n"/>
-      <c r="S69" s="5" t="n"/>
+      <c r="J69" s="5" t="n">
+        <v>31563.5</v>
+      </c>
+      <c r="K69" s="8">
+        <f>IF(AND(I69&lt;&gt;"",J69&lt;&gt;"",F69&lt;&gt;""), (J69-F69)/(F69-I69), "")</f>
+        <v/>
+      </c>
+      <c r="L69" s="8">
+        <f>IF(AND(F69&lt;&gt;"",G69&lt;&gt;"",I69&lt;&gt;""), (G69-F69)/(F69-I69), "")</f>
+        <v/>
+      </c>
+      <c r="M69" s="5">
+        <f>IF(N69&gt;0,"Win",IF(N69&lt;0,"Loss",""))</f>
+        <v/>
+      </c>
+      <c r="N69" s="16">
+        <f>IF(AND(F69&lt;&gt;"",G69&lt;&gt;"",H69&lt;&gt;"",D69&lt;&gt;""), IF(E69="Long", (G69-F69)*H69*VLOOKUP(D69,Multipliers!A:B,2,FALSE), (F69-G69)*H69*VLOOKUP(D69,Multipliers!A:B,2,FALSE)), "")</f>
+        <v/>
+      </c>
+      <c r="O69" s="9">
+        <f>IF(AND(N69&lt;&gt;"",F69&lt;&gt;"",H69&lt;&gt;"",D69&lt;&gt;""), N69/(F69*H69*VLOOKUP(D69,Multipliers!A:B,2,FALSE)), "")</f>
+        <v/>
+      </c>
+      <c r="P69" s="5">
+        <f>P68+N69</f>
+        <v/>
+      </c>
+      <c r="Q69" s="5" t="inlineStr">
+        <is>
+          <t>Break and Retest</t>
+        </is>
+      </c>
+      <c r="R69" s="5" t="inlineStr">
+        <is>
+          <t>Imported from Tradovate</t>
+        </is>
+      </c>
+      <c r="S69" s="5" t="inlineStr">
+        <is>
+          <t>MNQ</t>
+        </is>
+      </c>
       <c r="T69" s="5" t="n"/>
       <c r="U69" s="5" t="n"/>
       <c r="V69" s="5" t="n"/>
@@ -6036,25 +6408,77 @@
       <c r="AA69" s="5" t="n"/>
     </row>
     <row r="70" ht="15.75" customHeight="1">
-      <c r="A70" s="5" t="n"/>
-      <c r="B70" s="13" t="n"/>
-      <c r="C70" s="10" t="n"/>
-      <c r="D70" s="5" t="n"/>
-      <c r="E70" s="5" t="n"/>
-      <c r="F70" s="5" t="n"/>
-      <c r="G70" s="5" t="n"/>
-      <c r="H70" s="5" t="n"/>
+      <c r="A70" s="5" t="n">
+        <v>69</v>
+      </c>
+      <c r="B70" s="23" t="n">
+        <v>46301</v>
+      </c>
+      <c r="C70" s="10" t="n">
+        <v>0.4337268518518518</v>
+      </c>
+      <c r="D70" s="5" t="inlineStr">
+        <is>
+          <t>MGC</t>
+        </is>
+      </c>
+      <c r="E70" s="5" t="inlineStr">
+        <is>
+          <t>Short</t>
+        </is>
+      </c>
+      <c r="F70" s="5" t="n">
+        <v>4174.55</v>
+      </c>
+      <c r="G70" s="5" t="n">
+        <v>4181.4</v>
+      </c>
+      <c r="H70" s="5" t="n">
+        <v>2</v>
+      </c>
       <c r="I70" s="5" t="n"/>
-      <c r="J70" s="5" t="n"/>
-      <c r="K70" s="8" t="n"/>
-      <c r="L70" s="8" t="n"/>
-      <c r="M70" s="5" t="n"/>
-      <c r="N70" s="16" t="n"/>
-      <c r="O70" s="9" t="n"/>
-      <c r="P70" s="5" t="n"/>
-      <c r="Q70" s="5" t="n"/>
-      <c r="R70" s="5" t="n"/>
-      <c r="S70" s="5" t="n"/>
+      <c r="J70" s="5" t="n">
+        <v>4174.2</v>
+      </c>
+      <c r="K70" s="8">
+        <f>IF(AND(I70&lt;&gt;"",J70&lt;&gt;"",F70&lt;&gt;""), (J70-F70)/(F70-I70), "")</f>
+        <v/>
+      </c>
+      <c r="L70" s="8">
+        <f>IF(AND(F70&lt;&gt;"",G70&lt;&gt;"",I70&lt;&gt;""), (G70-F70)/(F70-I70), "")</f>
+        <v/>
+      </c>
+      <c r="M70" s="5">
+        <f>IF(N70&gt;0,"Win",IF(N70&lt;0,"Loss",""))</f>
+        <v/>
+      </c>
+      <c r="N70" s="16">
+        <f>IF(AND(F70&lt;&gt;"",G70&lt;&gt;"",H70&lt;&gt;"",D70&lt;&gt;""), IF(E70="Long", (G70-F70)*H70*VLOOKUP(D70,Multipliers!A:B,2,FALSE), (F70-G70)*H70*VLOOKUP(D70,Multipliers!A:B,2,FALSE)), "")</f>
+        <v/>
+      </c>
+      <c r="O70" s="9">
+        <f>IF(AND(N70&lt;&gt;"",F70&lt;&gt;"",H70&lt;&gt;"",D70&lt;&gt;""), N70/(F70*H70*VLOOKUP(D70,Multipliers!A:B,2,FALSE)), "")</f>
+        <v/>
+      </c>
+      <c r="P70" s="5">
+        <f>P69+N70</f>
+        <v/>
+      </c>
+      <c r="Q70" s="5" t="inlineStr">
+        <is>
+          <t>Break and Retest</t>
+        </is>
+      </c>
+      <c r="R70" s="5" t="inlineStr">
+        <is>
+          <t>Imported from Tradovate</t>
+        </is>
+      </c>
+      <c r="S70" s="5" t="inlineStr">
+        <is>
+          <t>MGC</t>
+        </is>
+      </c>
       <c r="T70" s="5" t="n"/>
       <c r="U70" s="5" t="n"/>
       <c r="V70" s="5" t="n"/>
@@ -6065,25 +6489,77 @@
       <c r="AA70" s="5" t="n"/>
     </row>
     <row r="71" ht="15.75" customHeight="1">
-      <c r="A71" s="5" t="n"/>
-      <c r="B71" s="13" t="n"/>
-      <c r="C71" s="10" t="n"/>
-      <c r="D71" s="5" t="n"/>
-      <c r="E71" s="5" t="n"/>
-      <c r="F71" s="5" t="n"/>
-      <c r="G71" s="5" t="n"/>
-      <c r="H71" s="5" t="n"/>
+      <c r="A71" s="5" t="n">
+        <v>70</v>
+      </c>
+      <c r="B71" s="23" t="n">
+        <v>46301</v>
+      </c>
+      <c r="C71" s="10" t="n">
+        <v>0.5335763888888889</v>
+      </c>
+      <c r="D71" s="5" t="inlineStr">
+        <is>
+          <t>MNQ</t>
+        </is>
+      </c>
+      <c r="E71" s="5" t="inlineStr">
+        <is>
+          <t>Long</t>
+        </is>
+      </c>
+      <c r="F71" s="5" t="n">
+        <v>31537.75</v>
+      </c>
+      <c r="G71" s="5" t="n">
+        <v>31543.5</v>
+      </c>
+      <c r="H71" s="5" t="n">
+        <v>1</v>
+      </c>
       <c r="I71" s="5" t="n"/>
-      <c r="J71" s="5" t="n"/>
-      <c r="K71" s="8" t="n"/>
-      <c r="L71" s="8" t="n"/>
-      <c r="M71" s="5" t="n"/>
-      <c r="N71" s="16" t="n"/>
-      <c r="O71" s="9" t="n"/>
-      <c r="P71" s="5" t="n"/>
-      <c r="Q71" s="5" t="n"/>
-      <c r="R71" s="5" t="n"/>
-      <c r="S71" s="5" t="n"/>
+      <c r="J71" s="5" t="n">
+        <v>31543.5</v>
+      </c>
+      <c r="K71" s="8">
+        <f>IF(AND(I71&lt;&gt;"",J71&lt;&gt;"",F71&lt;&gt;""), (J71-F71)/(F71-I71), "")</f>
+        <v/>
+      </c>
+      <c r="L71" s="8">
+        <f>IF(AND(F71&lt;&gt;"",G71&lt;&gt;"",I71&lt;&gt;""), (G71-F71)/(F71-I71), "")</f>
+        <v/>
+      </c>
+      <c r="M71" s="5">
+        <f>IF(N71&gt;0,"Win",IF(N71&lt;0,"Loss",""))</f>
+        <v/>
+      </c>
+      <c r="N71" s="16">
+        <f>IF(AND(F71&lt;&gt;"",G71&lt;&gt;"",H71&lt;&gt;"",D71&lt;&gt;""), IF(E71="Long", (G71-F71)*H71*VLOOKUP(D71,Multipliers!A:B,2,FALSE), (F71-G71)*H71*VLOOKUP(D71,Multipliers!A:B,2,FALSE)), "")</f>
+        <v/>
+      </c>
+      <c r="O71" s="9">
+        <f>IF(AND(N71&lt;&gt;"",F71&lt;&gt;"",H71&lt;&gt;"",D71&lt;&gt;""), N71/(F71*H71*VLOOKUP(D71,Multipliers!A:B,2,FALSE)), "")</f>
+        <v/>
+      </c>
+      <c r="P71" s="5">
+        <f>P70+N71</f>
+        <v/>
+      </c>
+      <c r="Q71" s="5" t="inlineStr">
+        <is>
+          <t>Break and Retest</t>
+        </is>
+      </c>
+      <c r="R71" s="5" t="inlineStr">
+        <is>
+          <t>Imported from Tradovate</t>
+        </is>
+      </c>
+      <c r="S71" s="5" t="inlineStr">
+        <is>
+          <t>MNQ</t>
+        </is>
+      </c>
       <c r="T71" s="5" t="n"/>
       <c r="U71" s="5" t="n"/>
       <c r="V71" s="5" t="n"/>
@@ -6094,25 +6570,77 @@
       <c r="AA71" s="5" t="n"/>
     </row>
     <row r="72" ht="15.75" customHeight="1">
-      <c r="A72" s="5" t="n"/>
-      <c r="B72" s="13" t="n"/>
-      <c r="C72" s="10" t="n"/>
-      <c r="D72" s="5" t="n"/>
-      <c r="E72" s="5" t="n"/>
-      <c r="F72" s="5" t="n"/>
-      <c r="G72" s="5" t="n"/>
-      <c r="H72" s="5" t="n"/>
+      <c r="A72" s="5" t="n">
+        <v>71</v>
+      </c>
+      <c r="B72" s="23" t="n">
+        <v>46301</v>
+      </c>
+      <c r="C72" s="10" t="n">
+        <v>0.5842708333333333</v>
+      </c>
+      <c r="D72" s="5" t="inlineStr">
+        <is>
+          <t>MNQ</t>
+        </is>
+      </c>
+      <c r="E72" s="5" t="inlineStr">
+        <is>
+          <t>Short</t>
+        </is>
+      </c>
+      <c r="F72" s="5" t="n">
+        <v>31530.75</v>
+      </c>
+      <c r="G72" s="5" t="n">
+        <v>31514.5</v>
+      </c>
+      <c r="H72" s="5" t="n">
+        <v>1</v>
+      </c>
       <c r="I72" s="5" t="n"/>
-      <c r="J72" s="5" t="n"/>
-      <c r="K72" s="8" t="n"/>
-      <c r="L72" s="8" t="n"/>
-      <c r="M72" s="5" t="n"/>
-      <c r="N72" s="16" t="n"/>
-      <c r="O72" s="9" t="n"/>
-      <c r="P72" s="5" t="n"/>
-      <c r="Q72" s="5" t="n"/>
-      <c r="R72" s="5" t="n"/>
-      <c r="S72" s="5" t="n"/>
+      <c r="J72" s="5" t="n">
+        <v>31514.5</v>
+      </c>
+      <c r="K72" s="8">
+        <f>IF(AND(I72&lt;&gt;"",J72&lt;&gt;"",F72&lt;&gt;""), (J72-F72)/(F72-I72), "")</f>
+        <v/>
+      </c>
+      <c r="L72" s="8">
+        <f>IF(AND(F72&lt;&gt;"",G72&lt;&gt;"",I72&lt;&gt;""), (G72-F72)/(F72-I72), "")</f>
+        <v/>
+      </c>
+      <c r="M72" s="5">
+        <f>IF(N72&gt;0,"Win",IF(N72&lt;0,"Loss",""))</f>
+        <v/>
+      </c>
+      <c r="N72" s="16">
+        <f>IF(AND(F72&lt;&gt;"",G72&lt;&gt;"",H72&lt;&gt;"",D72&lt;&gt;""), IF(E72="Long", (G72-F72)*H72*VLOOKUP(D72,Multipliers!A:B,2,FALSE), (F72-G72)*H72*VLOOKUP(D72,Multipliers!A:B,2,FALSE)), "")</f>
+        <v/>
+      </c>
+      <c r="O72" s="9">
+        <f>IF(AND(N72&lt;&gt;"",F72&lt;&gt;"",H72&lt;&gt;"",D72&lt;&gt;""), N72/(F72*H72*VLOOKUP(D72,Multipliers!A:B,2,FALSE)), "")</f>
+        <v/>
+      </c>
+      <c r="P72" s="5">
+        <f>P71+N72</f>
+        <v/>
+      </c>
+      <c r="Q72" s="5" t="inlineStr">
+        <is>
+          <t>Break and Retest</t>
+        </is>
+      </c>
+      <c r="R72" s="5" t="inlineStr">
+        <is>
+          <t>Imported from Tradovate</t>
+        </is>
+      </c>
+      <c r="S72" s="5" t="inlineStr">
+        <is>
+          <t>MNQ</t>
+        </is>
+      </c>
       <c r="T72" s="5" t="n"/>
       <c r="U72" s="5" t="n"/>
       <c r="V72" s="5" t="n"/>
@@ -6123,25 +6651,77 @@
       <c r="AA72" s="5" t="n"/>
     </row>
     <row r="73" ht="15.75" customHeight="1">
-      <c r="A73" s="5" t="n"/>
-      <c r="B73" s="13" t="n"/>
-      <c r="C73" s="10" t="n"/>
-      <c r="D73" s="5" t="n"/>
-      <c r="E73" s="5" t="n"/>
-      <c r="F73" s="5" t="n"/>
-      <c r="G73" s="5" t="n"/>
-      <c r="H73" s="5" t="n"/>
+      <c r="A73" s="5" t="n">
+        <v>72</v>
+      </c>
+      <c r="B73" s="23" t="n">
+        <v>46301</v>
+      </c>
+      <c r="C73" s="10" t="n">
+        <v>0.6289583333333333</v>
+      </c>
+      <c r="D73" s="5" t="inlineStr">
+        <is>
+          <t>MNQ</t>
+        </is>
+      </c>
+      <c r="E73" s="5" t="inlineStr">
+        <is>
+          <t>Short</t>
+        </is>
+      </c>
+      <c r="F73" s="5" t="n">
+        <v>31533</v>
+      </c>
+      <c r="G73" s="5" t="n">
+        <v>31507</v>
+      </c>
+      <c r="H73" s="5" t="n">
+        <v>1</v>
+      </c>
       <c r="I73" s="5" t="n"/>
-      <c r="J73" s="5" t="n"/>
-      <c r="K73" s="8" t="n"/>
-      <c r="L73" s="8" t="n"/>
-      <c r="M73" s="5" t="n"/>
-      <c r="N73" s="16" t="n"/>
-      <c r="O73" s="9" t="n"/>
-      <c r="P73" s="5" t="n"/>
-      <c r="Q73" s="5" t="n"/>
-      <c r="R73" s="5" t="n"/>
-      <c r="S73" s="5" t="n"/>
+      <c r="J73" s="5" t="n">
+        <v>31507</v>
+      </c>
+      <c r="K73" s="8">
+        <f>IF(AND(I73&lt;&gt;"",J73&lt;&gt;"",F73&lt;&gt;""), (J73-F73)/(F73-I73), "")</f>
+        <v/>
+      </c>
+      <c r="L73" s="8">
+        <f>IF(AND(F73&lt;&gt;"",G73&lt;&gt;"",I73&lt;&gt;""), (G73-F73)/(F73-I73), "")</f>
+        <v/>
+      </c>
+      <c r="M73" s="5">
+        <f>IF(N73&gt;0,"Win",IF(N73&lt;0,"Loss",""))</f>
+        <v/>
+      </c>
+      <c r="N73" s="16">
+        <f>IF(AND(F73&lt;&gt;"",G73&lt;&gt;"",H73&lt;&gt;"",D73&lt;&gt;""), IF(E73="Long", (G73-F73)*H73*VLOOKUP(D73,Multipliers!A:B,2,FALSE), (F73-G73)*H73*VLOOKUP(D73,Multipliers!A:B,2,FALSE)), "")</f>
+        <v/>
+      </c>
+      <c r="O73" s="9">
+        <f>IF(AND(N73&lt;&gt;"",F73&lt;&gt;"",H73&lt;&gt;"",D73&lt;&gt;""), N73/(F73*H73*VLOOKUP(D73,Multipliers!A:B,2,FALSE)), "")</f>
+        <v/>
+      </c>
+      <c r="P73" s="5">
+        <f>P72+N73</f>
+        <v/>
+      </c>
+      <c r="Q73" s="5" t="inlineStr">
+        <is>
+          <t>Break and Retest</t>
+        </is>
+      </c>
+      <c r="R73" s="5" t="inlineStr">
+        <is>
+          <t>Imported from Tradovate</t>
+        </is>
+      </c>
+      <c r="S73" s="5" t="inlineStr">
+        <is>
+          <t>MNQ</t>
+        </is>
+      </c>
       <c r="T73" s="5" t="n"/>
       <c r="U73" s="5" t="n"/>
       <c r="V73" s="5" t="n"/>
@@ -6152,25 +6732,77 @@
       <c r="AA73" s="5" t="n"/>
     </row>
     <row r="74" ht="15.75" customHeight="1">
-      <c r="A74" s="5" t="n"/>
-      <c r="B74" s="13" t="n"/>
-      <c r="C74" s="10" t="n"/>
-      <c r="D74" s="5" t="n"/>
-      <c r="E74" s="5" t="n"/>
-      <c r="F74" s="5" t="n"/>
-      <c r="G74" s="5" t="n"/>
-      <c r="H74" s="5" t="n"/>
+      <c r="A74" s="5" t="n">
+        <v>73</v>
+      </c>
+      <c r="B74" s="23" t="n">
+        <v>46302</v>
+      </c>
+      <c r="C74" s="10" t="n">
+        <v>0.4063541666666667</v>
+      </c>
+      <c r="D74" s="5" t="inlineStr">
+        <is>
+          <t>MES</t>
+        </is>
+      </c>
+      <c r="E74" s="5" t="inlineStr">
+        <is>
+          <t>Short</t>
+        </is>
+      </c>
+      <c r="F74" s="5" t="n">
+        <v>7828.5</v>
+      </c>
+      <c r="G74" s="5" t="n">
+        <v>7828</v>
+      </c>
+      <c r="H74" s="5" t="n">
+        <v>2</v>
+      </c>
       <c r="I74" s="5" t="n"/>
-      <c r="J74" s="5" t="n"/>
-      <c r="K74" s="8" t="n"/>
-      <c r="L74" s="8" t="n"/>
-      <c r="M74" s="5" t="n"/>
-      <c r="N74" s="16" t="n"/>
-      <c r="O74" s="9" t="n"/>
-      <c r="P74" s="5" t="n"/>
-      <c r="Q74" s="5" t="n"/>
-      <c r="R74" s="5" t="n"/>
-      <c r="S74" s="5" t="n"/>
+      <c r="J74" s="5" t="n">
+        <v>7828</v>
+      </c>
+      <c r="K74" s="8">
+        <f>IF(AND(I74&lt;&gt;"",J74&lt;&gt;"",F74&lt;&gt;""), (J74-F74)/(F74-I74), "")</f>
+        <v/>
+      </c>
+      <c r="L74" s="8">
+        <f>IF(AND(F74&lt;&gt;"",G74&lt;&gt;"",I74&lt;&gt;""), (G74-F74)/(F74-I74), "")</f>
+        <v/>
+      </c>
+      <c r="M74" s="5">
+        <f>IF(N74&gt;0,"Win",IF(N74&lt;0,"Loss",""))</f>
+        <v/>
+      </c>
+      <c r="N74" s="16">
+        <f>IF(AND(F74&lt;&gt;"",G74&lt;&gt;"",H74&lt;&gt;"",D74&lt;&gt;""), IF(E74="Long", (G74-F74)*H74*VLOOKUP(D74,Multipliers!A:B,2,FALSE), (F74-G74)*H74*VLOOKUP(D74,Multipliers!A:B,2,FALSE)), "")</f>
+        <v/>
+      </c>
+      <c r="O74" s="9">
+        <f>IF(AND(N74&lt;&gt;"",F74&lt;&gt;"",H74&lt;&gt;"",D74&lt;&gt;""), N74/(F74*H74*VLOOKUP(D74,Multipliers!A:B,2,FALSE)), "")</f>
+        <v/>
+      </c>
+      <c r="P74" s="5">
+        <f>P73+N74</f>
+        <v/>
+      </c>
+      <c r="Q74" s="5" t="inlineStr">
+        <is>
+          <t>Break and Retest</t>
+        </is>
+      </c>
+      <c r="R74" s="5" t="inlineStr">
+        <is>
+          <t>Imported from Tradovate</t>
+        </is>
+      </c>
+      <c r="S74" s="5" t="inlineStr">
+        <is>
+          <t>MES</t>
+        </is>
+      </c>
       <c r="T74" s="5" t="n"/>
       <c r="U74" s="5" t="n"/>
       <c r="V74" s="5" t="n"/>
@@ -6181,25 +6813,79 @@
       <c r="AA74" s="5" t="n"/>
     </row>
     <row r="75" ht="15.75" customHeight="1">
-      <c r="A75" s="5" t="n"/>
-      <c r="B75" s="13" t="n"/>
-      <c r="C75" s="10" t="n"/>
-      <c r="D75" s="5" t="n"/>
-      <c r="E75" s="5" t="n"/>
-      <c r="F75" s="5" t="n"/>
-      <c r="G75" s="5" t="n"/>
-      <c r="H75" s="5" t="n"/>
-      <c r="I75" s="5" t="n"/>
-      <c r="J75" s="5" t="n"/>
-      <c r="K75" s="8" t="n"/>
-      <c r="L75" s="8" t="n"/>
-      <c r="M75" s="5" t="n"/>
-      <c r="N75" s="16" t="n"/>
-      <c r="O75" s="9" t="n"/>
-      <c r="P75" s="5" t="n"/>
-      <c r="Q75" s="5" t="n"/>
-      <c r="R75" s="5" t="n"/>
-      <c r="S75" s="5" t="n"/>
+      <c r="A75" s="5" t="n">
+        <v>74</v>
+      </c>
+      <c r="B75" s="23" t="n">
+        <v>46302</v>
+      </c>
+      <c r="C75" s="10" t="n">
+        <v>0.4418055555555556</v>
+      </c>
+      <c r="D75" s="5" t="inlineStr">
+        <is>
+          <t>MGC</t>
+        </is>
+      </c>
+      <c r="E75" s="5" t="inlineStr">
+        <is>
+          <t>Long</t>
+        </is>
+      </c>
+      <c r="F75" s="5" t="n">
+        <v>4132.3</v>
+      </c>
+      <c r="G75" s="5" t="n">
+        <v>4128.1</v>
+      </c>
+      <c r="H75" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="I75" s="5" t="n">
+        <v>4128.1</v>
+      </c>
+      <c r="J75" s="5" t="n">
+        <v>4138.1</v>
+      </c>
+      <c r="K75" s="8">
+        <f>IF(AND(I75&lt;&gt;"",J75&lt;&gt;"",F75&lt;&gt;""), (J75-F75)/(F75-I75), "")</f>
+        <v/>
+      </c>
+      <c r="L75" s="8">
+        <f>IF(AND(F75&lt;&gt;"",G75&lt;&gt;"",I75&lt;&gt;""), (G75-F75)/(F75-I75), "")</f>
+        <v/>
+      </c>
+      <c r="M75" s="5">
+        <f>IF(N75&gt;0,"Win",IF(N75&lt;0,"Loss",""))</f>
+        <v/>
+      </c>
+      <c r="N75" s="16">
+        <f>IF(AND(F75&lt;&gt;"",G75&lt;&gt;"",H75&lt;&gt;"",D75&lt;&gt;""), IF(E75="Long", (G75-F75)*H75*VLOOKUP(D75,Multipliers!A:B,2,FALSE), (F75-G75)*H75*VLOOKUP(D75,Multipliers!A:B,2,FALSE)), "")</f>
+        <v/>
+      </c>
+      <c r="O75" s="9">
+        <f>IF(AND(N75&lt;&gt;"",F75&lt;&gt;"",H75&lt;&gt;"",D75&lt;&gt;""), N75/(F75*H75*VLOOKUP(D75,Multipliers!A:B,2,FALSE)), "")</f>
+        <v/>
+      </c>
+      <c r="P75" s="5">
+        <f>P74+N75</f>
+        <v/>
+      </c>
+      <c r="Q75" s="5" t="inlineStr">
+        <is>
+          <t>Break and Retest</t>
+        </is>
+      </c>
+      <c r="R75" s="5" t="inlineStr">
+        <is>
+          <t>Imported from Tradovate</t>
+        </is>
+      </c>
+      <c r="S75" s="5" t="inlineStr">
+        <is>
+          <t>MGC</t>
+        </is>
+      </c>
       <c r="T75" s="5" t="n"/>
       <c r="U75" s="5" t="n"/>
       <c r="V75" s="5" t="n"/>
@@ -6210,25 +6896,77 @@
       <c r="AA75" s="5" t="n"/>
     </row>
     <row r="76" ht="15.75" customHeight="1">
-      <c r="A76" s="5" t="n"/>
-      <c r="B76" s="13" t="n"/>
-      <c r="C76" s="10" t="n"/>
-      <c r="D76" s="5" t="n"/>
-      <c r="E76" s="5" t="n"/>
-      <c r="F76" s="5" t="n"/>
-      <c r="G76" s="5" t="n"/>
-      <c r="H76" s="5" t="n"/>
+      <c r="A76" s="5" t="n">
+        <v>75</v>
+      </c>
+      <c r="B76" s="23" t="n">
+        <v>46302</v>
+      </c>
+      <c r="C76" s="10" t="n">
+        <v>0.4553125</v>
+      </c>
+      <c r="D76" s="5" t="inlineStr">
+        <is>
+          <t>MNQ</t>
+        </is>
+      </c>
+      <c r="E76" s="5" t="inlineStr">
+        <is>
+          <t>Short</t>
+        </is>
+      </c>
+      <c r="F76" s="5" t="n">
+        <v>31231.375</v>
+      </c>
+      <c r="G76" s="5" t="n">
+        <v>31228.75</v>
+      </c>
+      <c r="H76" s="5" t="n">
+        <v>2</v>
+      </c>
       <c r="I76" s="5" t="n"/>
-      <c r="J76" s="5" t="n"/>
-      <c r="K76" s="8" t="n"/>
-      <c r="L76" s="8" t="n"/>
-      <c r="M76" s="5" t="n"/>
-      <c r="N76" s="16" t="n"/>
-      <c r="O76" s="9" t="n"/>
-      <c r="P76" s="5" t="n"/>
-      <c r="Q76" s="5" t="n"/>
-      <c r="R76" s="5" t="n"/>
-      <c r="S76" s="5" t="n"/>
+      <c r="J76" s="5" t="n">
+        <v>31228.75</v>
+      </c>
+      <c r="K76" s="8">
+        <f>IF(AND(I76&lt;&gt;"",J76&lt;&gt;"",F76&lt;&gt;""), (J76-F76)/(F76-I76), "")</f>
+        <v/>
+      </c>
+      <c r="L76" s="8">
+        <f>IF(AND(F76&lt;&gt;"",G76&lt;&gt;"",I76&lt;&gt;""), (G76-F76)/(F76-I76), "")</f>
+        <v/>
+      </c>
+      <c r="M76" s="5">
+        <f>IF(N76&gt;0,"Win",IF(N76&lt;0,"Loss",""))</f>
+        <v/>
+      </c>
+      <c r="N76" s="16">
+        <f>IF(AND(F76&lt;&gt;"",G76&lt;&gt;"",H76&lt;&gt;"",D76&lt;&gt;""), IF(E76="Long", (G76-F76)*H76*VLOOKUP(D76,Multipliers!A:B,2,FALSE), (F76-G76)*H76*VLOOKUP(D76,Multipliers!A:B,2,FALSE)), "")</f>
+        <v/>
+      </c>
+      <c r="O76" s="9">
+        <f>IF(AND(N76&lt;&gt;"",F76&lt;&gt;"",H76&lt;&gt;"",D76&lt;&gt;""), N76/(F76*H76*VLOOKUP(D76,Multipliers!A:B,2,FALSE)), "")</f>
+        <v/>
+      </c>
+      <c r="P76" s="5">
+        <f>P75+N76</f>
+        <v/>
+      </c>
+      <c r="Q76" s="5" t="inlineStr">
+        <is>
+          <t>Break and Retest</t>
+        </is>
+      </c>
+      <c r="R76" s="5" t="inlineStr">
+        <is>
+          <t>Imported from Tradovate</t>
+        </is>
+      </c>
+      <c r="S76" s="5" t="inlineStr">
+        <is>
+          <t>MNQ</t>
+        </is>
+      </c>
       <c r="T76" s="5" t="n"/>
       <c r="U76" s="5" t="n"/>
       <c r="V76" s="5" t="n"/>
@@ -6239,25 +6977,77 @@
       <c r="AA76" s="5" t="n"/>
     </row>
     <row r="77" ht="15.75" customHeight="1">
-      <c r="A77" s="5" t="n"/>
-      <c r="B77" s="13" t="n"/>
-      <c r="C77" s="10" t="n"/>
-      <c r="D77" s="5" t="n"/>
-      <c r="E77" s="5" t="n"/>
-      <c r="F77" s="5" t="n"/>
-      <c r="G77" s="5" t="n"/>
-      <c r="H77" s="5" t="n"/>
+      <c r="A77" s="5" t="n">
+        <v>76</v>
+      </c>
+      <c r="B77" s="23" t="n">
+        <v>46302</v>
+      </c>
+      <c r="C77" s="10" t="n">
+        <v>0.4621643518518518</v>
+      </c>
+      <c r="D77" s="5" t="inlineStr">
+        <is>
+          <t>MGC</t>
+        </is>
+      </c>
+      <c r="E77" s="5" t="inlineStr">
+        <is>
+          <t>Short</t>
+        </is>
+      </c>
+      <c r="F77" s="5" t="n">
+        <v>4127.7</v>
+      </c>
+      <c r="G77" s="5" t="n">
+        <v>4127.3</v>
+      </c>
+      <c r="H77" s="5" t="n">
+        <v>1</v>
+      </c>
       <c r="I77" s="5" t="n"/>
-      <c r="J77" s="5" t="n"/>
-      <c r="K77" s="8" t="n"/>
-      <c r="L77" s="8" t="n"/>
-      <c r="M77" s="5" t="n"/>
-      <c r="N77" s="16" t="n"/>
-      <c r="O77" s="9" t="n"/>
-      <c r="P77" s="5" t="n"/>
-      <c r="Q77" s="5" t="n"/>
-      <c r="R77" s="5" t="n"/>
-      <c r="S77" s="5" t="n"/>
+      <c r="J77" s="5" t="n">
+        <v>4127.3</v>
+      </c>
+      <c r="K77" s="8">
+        <f>IF(AND(I77&lt;&gt;"",J77&lt;&gt;"",F77&lt;&gt;""), (J77-F77)/(F77-I77), "")</f>
+        <v/>
+      </c>
+      <c r="L77" s="8">
+        <f>IF(AND(F77&lt;&gt;"",G77&lt;&gt;"",I77&lt;&gt;""), (G77-F77)/(F77-I77), "")</f>
+        <v/>
+      </c>
+      <c r="M77" s="5">
+        <f>IF(N77&gt;0,"Win",IF(N77&lt;0,"Loss",""))</f>
+        <v/>
+      </c>
+      <c r="N77" s="16">
+        <f>IF(AND(F77&lt;&gt;"",G77&lt;&gt;"",H77&lt;&gt;"",D77&lt;&gt;""), IF(E77="Long", (G77-F77)*H77*VLOOKUP(D77,Multipliers!A:B,2,FALSE), (F77-G77)*H77*VLOOKUP(D77,Multipliers!A:B,2,FALSE)), "")</f>
+        <v/>
+      </c>
+      <c r="O77" s="9">
+        <f>IF(AND(N77&lt;&gt;"",F77&lt;&gt;"",H77&lt;&gt;"",D77&lt;&gt;""), N77/(F77*H77*VLOOKUP(D77,Multipliers!A:B,2,FALSE)), "")</f>
+        <v/>
+      </c>
+      <c r="P77" s="5">
+        <f>P76+N77</f>
+        <v/>
+      </c>
+      <c r="Q77" s="5" t="inlineStr">
+        <is>
+          <t>Break and Retest</t>
+        </is>
+      </c>
+      <c r="R77" s="5" t="inlineStr">
+        <is>
+          <t>Imported from Tradovate</t>
+        </is>
+      </c>
+      <c r="S77" s="5" t="inlineStr">
+        <is>
+          <t>MGC</t>
+        </is>
+      </c>
       <c r="T77" s="5" t="n"/>
       <c r="U77" s="5" t="n"/>
       <c r="V77" s="5" t="n"/>
@@ -34762,1984 +35552,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E79"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="30" customWidth="1" min="1" max="1"/>
-    <col width="14" customWidth="1" min="2" max="2"/>
-    <col width="14" customWidth="1" min="3" max="3"/>
-    <col width="14" customWidth="1" min="4" max="4"/>
-    <col width="14" customWidth="1" min="5" max="5"/>
-    <col width="14" customWidth="1" min="6" max="6"/>
-    <col width="14" customWidth="1" min="7" max="7"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="25" t="inlineStr">
-        <is>
-          <t>Overview</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>Generated</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>2026-10-02 10:51</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>Date range</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>2026-09-23 → 2026-10-02</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>Trades</t>
-        </is>
-      </c>
-      <c r="B4" t="n">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>Win rate</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>60.7%</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>Total P&amp;L</t>
-        </is>
-      </c>
-      <c r="B6" t="n">
-        <v>-511.75</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>Profit factor</t>
-        </is>
-      </c>
-      <c r="B7" t="n">
-        <v>0.84</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>Expectancy / trade</t>
-        </is>
-      </c>
-      <c r="B8" t="n">
-        <v>-8.390000000000001</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>Avg win</t>
-        </is>
-      </c>
-      <c r="B9" t="n">
-        <v>73.06</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>Avg loss</t>
-        </is>
-      </c>
-      <c r="B10" t="n">
-        <v>-133.96</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>Avg RR targeted</t>
-        </is>
-      </c>
-      <c r="B11" t="n">
-        <v>1.32</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>Avg RR realized</t>
-        </is>
-      </c>
-      <c r="B12" t="n">
-        <v>0.25</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>Max drawdown</t>
-        </is>
-      </c>
-      <c r="B13" t="n">
-        <v>-1656</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>Max win streak</t>
-        </is>
-      </c>
-      <c r="B14" t="n">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>Max loss streak</t>
-        </is>
-      </c>
-      <c r="B15" t="n">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="25" t="inlineStr">
-        <is>
-          <t>By Setup</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="24" t="inlineStr">
-        <is>
-          <t>Setup</t>
-        </is>
-      </c>
-      <c r="B18" s="24" t="inlineStr">
-        <is>
-          <t>Trades</t>
-        </is>
-      </c>
-      <c r="C18" s="24" t="inlineStr">
-        <is>
-          <t>Win %</t>
-        </is>
-      </c>
-      <c r="D18" s="24" t="inlineStr">
-        <is>
-          <t>Total P&amp;L</t>
-        </is>
-      </c>
-      <c r="E18" s="24" t="inlineStr">
-        <is>
-          <t>Expectancy</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>Break and Retest</t>
-        </is>
-      </c>
-      <c r="B19" t="n">
-        <v>61</v>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>61%</t>
-        </is>
-      </c>
-      <c r="D19" t="n">
-        <v>-511.75</v>
-      </c>
-      <c r="E19" t="n">
-        <v>-8.390000000000001</v>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="25" t="inlineStr">
-        <is>
-          <t>By Instrument</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="24" t="inlineStr">
-        <is>
-          <t>Instrument</t>
-        </is>
-      </c>
-      <c r="B22" s="24" t="inlineStr">
-        <is>
-          <t>Trades</t>
-        </is>
-      </c>
-      <c r="C22" s="24" t="inlineStr">
-        <is>
-          <t>Win %</t>
-        </is>
-      </c>
-      <c r="D22" s="24" t="inlineStr">
-        <is>
-          <t>Total P&amp;L</t>
-        </is>
-      </c>
-      <c r="E22" s="24" t="inlineStr">
-        <is>
-          <t>Expectancy</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>MNQ</t>
-        </is>
-      </c>
-      <c r="B23" t="n">
-        <v>25</v>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>64%</t>
-        </is>
-      </c>
-      <c r="D23" t="n">
-        <v>819</v>
-      </c>
-      <c r="E23" t="n">
-        <v>32.76</v>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>MYM</t>
-        </is>
-      </c>
-      <c r="B24" t="n">
-        <v>11</v>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>45%</t>
-        </is>
-      </c>
-      <c r="D24" t="n">
-        <v>-104</v>
-      </c>
-      <c r="E24" t="n">
-        <v>-9.449999999999999</v>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>MES</t>
-        </is>
-      </c>
-      <c r="B25" t="n">
-        <v>11</v>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>55%</t>
-        </is>
-      </c>
-      <c r="D25" t="n">
-        <v>-183.75</v>
-      </c>
-      <c r="E25" t="n">
-        <v>-16.7</v>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>MGC</t>
-        </is>
-      </c>
-      <c r="B26" t="n">
-        <v>14</v>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>71%</t>
-        </is>
-      </c>
-      <c r="D26" t="n">
-        <v>-1043</v>
-      </c>
-      <c r="E26" t="n">
-        <v>-74.5</v>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="25" t="inlineStr">
-        <is>
-          <t>By Direction</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" s="24" t="inlineStr">
-        <is>
-          <t>Direction</t>
-        </is>
-      </c>
-      <c r="B29" s="24" t="inlineStr">
-        <is>
-          <t>Trades</t>
-        </is>
-      </c>
-      <c r="C29" s="24" t="inlineStr">
-        <is>
-          <t>Win %</t>
-        </is>
-      </c>
-      <c r="D29" s="24" t="inlineStr">
-        <is>
-          <t>Total P&amp;L</t>
-        </is>
-      </c>
-      <c r="E29" s="24" t="inlineStr">
-        <is>
-          <t>Expectancy</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>Short</t>
-        </is>
-      </c>
-      <c r="B30" t="n">
-        <v>34</v>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>62%</t>
-        </is>
-      </c>
-      <c r="D30" t="n">
-        <v>747.5</v>
-      </c>
-      <c r="E30" t="n">
-        <v>21.99</v>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>Long</t>
-        </is>
-      </c>
-      <c r="B31" t="n">
-        <v>27</v>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>59%</t>
-        </is>
-      </c>
-      <c r="D31" t="n">
-        <v>-1259.25</v>
-      </c>
-      <c r="E31" t="n">
-        <v>-46.64</v>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" s="25" t="inlineStr">
-        <is>
-          <t>By Hour</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" s="24" t="inlineStr">
-        <is>
-          <t>Hour</t>
-        </is>
-      </c>
-      <c r="B34" s="24" t="inlineStr">
-        <is>
-          <t>Trades</t>
-        </is>
-      </c>
-      <c r="C34" s="24" t="inlineStr">
-        <is>
-          <t>Win %</t>
-        </is>
-      </c>
-      <c r="D34" s="24" t="inlineStr">
-        <is>
-          <t>Total P&amp;L</t>
-        </is>
-      </c>
-      <c r="E34" s="24" t="inlineStr">
-        <is>
-          <t>Expectancy</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" t="inlineStr">
-        <is>
-          <t>08:00</t>
-        </is>
-      </c>
-      <c r="B35" t="n">
-        <v>1</v>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="D35" t="n">
-        <v>14</v>
-      </c>
-      <c r="E35" t="n">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" t="inlineStr">
-        <is>
-          <t>09:00</t>
-        </is>
-      </c>
-      <c r="B36" t="n">
-        <v>9</v>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>44%</t>
-        </is>
-      </c>
-      <c r="D36" t="n">
-        <v>-11</v>
-      </c>
-      <c r="E36" t="n">
-        <v>-1.22</v>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" t="inlineStr">
-        <is>
-          <t>10:00</t>
-        </is>
-      </c>
-      <c r="B37" t="n">
-        <v>28</v>
-      </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>54%</t>
-        </is>
-      </c>
-      <c r="D37" t="n">
-        <v>203</v>
-      </c>
-      <c r="E37" t="n">
-        <v>7.25</v>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" t="inlineStr">
-        <is>
-          <t>11:00</t>
-        </is>
-      </c>
-      <c r="B38" t="n">
-        <v>10</v>
-      </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>70%</t>
-        </is>
-      </c>
-      <c r="D38" t="n">
-        <v>282</v>
-      </c>
-      <c r="E38" t="n">
-        <v>28.2</v>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" t="inlineStr">
-        <is>
-          <t>13:00</t>
-        </is>
-      </c>
-      <c r="B39" t="n">
-        <v>7</v>
-      </c>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>71%</t>
-        </is>
-      </c>
-      <c r="D39" t="n">
-        <v>158.5</v>
-      </c>
-      <c r="E39" t="n">
-        <v>22.64</v>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" t="inlineStr">
-        <is>
-          <t>14:00</t>
-        </is>
-      </c>
-      <c r="B40" t="n">
-        <v>3</v>
-      </c>
-      <c r="C40" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="D40" t="n">
-        <v>31.75</v>
-      </c>
-      <c r="E40" t="n">
-        <v>10.58</v>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" t="inlineStr">
-        <is>
-          <t>22:00</t>
-        </is>
-      </c>
-      <c r="B41" t="n">
-        <v>1</v>
-      </c>
-      <c r="C41" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="D41" t="n">
-        <v>114</v>
-      </c>
-      <c r="E41" t="n">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" t="inlineStr">
-        <is>
-          <t>23:00</t>
-        </is>
-      </c>
-      <c r="B42" t="n">
-        <v>2</v>
-      </c>
-      <c r="C42" t="inlineStr">
-        <is>
-          <t>50%</t>
-        </is>
-      </c>
-      <c r="D42" t="n">
-        <v>-1304</v>
-      </c>
-      <c r="E42" t="n">
-        <v>-652</v>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" s="25" t="inlineStr">
-        <is>
-          <t>By Day of Week</t>
-        </is>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" s="24" t="inlineStr">
-        <is>
-          <t>Day</t>
-        </is>
-      </c>
-      <c r="B45" s="24" t="inlineStr">
-        <is>
-          <t>Trades</t>
-        </is>
-      </c>
-      <c r="C45" s="24" t="inlineStr">
-        <is>
-          <t>Win %</t>
-        </is>
-      </c>
-      <c r="D45" s="24" t="inlineStr">
-        <is>
-          <t>Total P&amp;L</t>
-        </is>
-      </c>
-      <c r="E45" s="24" t="inlineStr">
-        <is>
-          <t>Expectancy</t>
-        </is>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" t="inlineStr">
-        <is>
-          <t>Thu</t>
-        </is>
-      </c>
-      <c r="B46" t="n">
-        <v>23</v>
-      </c>
-      <c r="C46" t="inlineStr">
-        <is>
-          <t>65%</t>
-        </is>
-      </c>
-      <c r="D46" t="n">
-        <v>622.25</v>
-      </c>
-      <c r="E46" t="n">
-        <v>27.05</v>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" t="inlineStr">
-        <is>
-          <t>Wed</t>
-        </is>
-      </c>
-      <c r="B47" t="n">
-        <v>12</v>
-      </c>
-      <c r="C47" t="inlineStr">
-        <is>
-          <t>83%</t>
-        </is>
-      </c>
-      <c r="D47" t="n">
-        <v>401</v>
-      </c>
-      <c r="E47" t="n">
-        <v>33.42</v>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" t="inlineStr">
-        <is>
-          <t>Mon</t>
-        </is>
-      </c>
-      <c r="B48" t="n">
-        <v>1</v>
-      </c>
-      <c r="C48" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="D48" t="n">
-        <v>5</v>
-      </c>
-      <c r="E48" t="n">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" t="inlineStr">
-        <is>
-          <t>Fri</t>
-        </is>
-      </c>
-      <c r="B49" t="n">
-        <v>12</v>
-      </c>
-      <c r="C49" t="inlineStr">
-        <is>
-          <t>42%</t>
-        </is>
-      </c>
-      <c r="D49" t="n">
-        <v>-136</v>
-      </c>
-      <c r="E49" t="n">
-        <v>-11.33</v>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" t="inlineStr">
-        <is>
-          <t>Tue</t>
-        </is>
-      </c>
-      <c r="B50" t="n">
-        <v>11</v>
-      </c>
-      <c r="C50" t="inlineStr">
-        <is>
-          <t>45%</t>
-        </is>
-      </c>
-      <c r="D50" t="n">
-        <v>-209</v>
-      </c>
-      <c r="E50" t="n">
-        <v>-19</v>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" t="inlineStr">
-        <is>
-          <t>Sun</t>
-        </is>
-      </c>
-      <c r="B51" t="n">
-        <v>2</v>
-      </c>
-      <c r="C51" t="inlineStr">
-        <is>
-          <t>50%</t>
-        </is>
-      </c>
-      <c r="D51" t="n">
-        <v>-1195</v>
-      </c>
-      <c r="E51" t="n">
-        <v>-597.5</v>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" s="25" t="inlineStr">
-        <is>
-          <t>Behavior Flags</t>
-        </is>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" t="inlineStr">
-        <is>
-          <t>Overtrading</t>
-        </is>
-      </c>
-      <c r="B54" t="inlineStr">
-        <is>
-          <t>9 trades on 2026-09-23 (&gt; 6)</t>
-        </is>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" t="inlineStr">
-        <is>
-          <t>Overtrading</t>
-        </is>
-      </c>
-      <c r="B55" t="inlineStr">
-        <is>
-          <t>11 trades on 2026-09-24 (&gt; 6)</t>
-        </is>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56" t="inlineStr">
-        <is>
-          <t>Overtrading</t>
-        </is>
-      </c>
-      <c r="B56" t="inlineStr">
-        <is>
-          <t>7 trades on 2026-09-25 (&gt; 6)</t>
-        </is>
-      </c>
-    </row>
-    <row r="57">
-      <c r="A57" t="inlineStr">
-        <is>
-          <t>Overtrading</t>
-        </is>
-      </c>
-      <c r="B57" t="inlineStr">
-        <is>
-          <t>11 trades on 2026-09-29 (&gt; 6)</t>
-        </is>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58" t="inlineStr">
-        <is>
-          <t>Overtrading</t>
-        </is>
-      </c>
-      <c r="B58" t="inlineStr">
-        <is>
-          <t>12 trades on 2026-10-01 (&gt; 6)</t>
-        </is>
-      </c>
-    </row>
-    <row r="59">
-      <c r="A59" t="inlineStr">
-        <is>
-          <t>Possible revenge trade</t>
-        </is>
-      </c>
-      <c r="B59" t="inlineStr">
-        <is>
-          <t>MGC Long at 09/23 10:32 — 11 min after a loss, size 3</t>
-        </is>
-      </c>
-    </row>
-    <row r="60">
-      <c r="A60" t="inlineStr">
-        <is>
-          <t>Possible revenge trade</t>
-        </is>
-      </c>
-      <c r="B60" t="inlineStr">
-        <is>
-          <t>MYM Long at 09/24 10:01 — 10 min after a loss, size 2</t>
-        </is>
-      </c>
-    </row>
-    <row r="61">
-      <c r="A61" t="inlineStr">
-        <is>
-          <t>Possible revenge trade</t>
-        </is>
-      </c>
-      <c r="B61" t="inlineStr">
-        <is>
-          <t>MYM Short at 09/24 10:32 — 2 min after a loss, size 4</t>
-        </is>
-      </c>
-    </row>
-    <row r="62">
-      <c r="A62" t="inlineStr">
-        <is>
-          <t>Possible revenge trade</t>
-        </is>
-      </c>
-      <c r="B62" t="inlineStr">
-        <is>
-          <t>MYM Long at 09/25 09:56 — 9 min after a loss, size 4</t>
-        </is>
-      </c>
-    </row>
-    <row r="63">
-      <c r="A63" t="inlineStr">
-        <is>
-          <t>Possible revenge trade</t>
-        </is>
-      </c>
-      <c r="B63" t="inlineStr">
-        <is>
-          <t>MNQ Long at 09/25 10:40 — 8 min after a loss, size 3</t>
-        </is>
-      </c>
-    </row>
-    <row r="64">
-      <c r="A64" t="inlineStr">
-        <is>
-          <t>Possible revenge trade</t>
-        </is>
-      </c>
-      <c r="B64" t="inlineStr">
-        <is>
-          <t>MNQ Short at 09/25 10:50 — 10 min after a loss, size 3</t>
-        </is>
-      </c>
-    </row>
-    <row r="65">
-      <c r="A65" t="inlineStr">
-        <is>
-          <t>Possible revenge trade</t>
-        </is>
-      </c>
-      <c r="B65" t="inlineStr">
-        <is>
-          <t>MNQ Short at 09/25 10:50 — 0 min after a loss, size 3</t>
-        </is>
-      </c>
-    </row>
-    <row r="66">
-      <c r="A66" t="inlineStr">
-        <is>
-          <t>Possible revenge trade</t>
-        </is>
-      </c>
-      <c r="B66" t="inlineStr">
-        <is>
-          <t>MYM Short at 09/29 10:00 — 13 min after a loss, size 2</t>
-        </is>
-      </c>
-    </row>
-    <row r="67">
-      <c r="A67" t="inlineStr">
-        <is>
-          <t>Possible revenge trade</t>
-        </is>
-      </c>
-      <c r="B67" t="inlineStr">
-        <is>
-          <t>MES Long at 09/29 10:18 — 12 min after a loss, size 3</t>
-        </is>
-      </c>
-    </row>
-    <row r="68">
-      <c r="A68" t="inlineStr">
-        <is>
-          <t>Possible revenge trade</t>
-        </is>
-      </c>
-      <c r="B68" t="inlineStr">
-        <is>
-          <t>MYM Short at 09/29 13:48 — 4 min after a loss, size 5</t>
-        </is>
-      </c>
-    </row>
-    <row r="69">
-      <c r="A69" t="inlineStr">
-        <is>
-          <t>Possible revenge trade</t>
-        </is>
-      </c>
-      <c r="B69" t="inlineStr">
-        <is>
-          <t>MNQ Short at 10/01 10:06 — 15 min after a loss, size 2</t>
-        </is>
-      </c>
-    </row>
-    <row r="70">
-      <c r="A70" t="inlineStr">
-        <is>
-          <t>Possible revenge trade</t>
-        </is>
-      </c>
-      <c r="B70" t="inlineStr">
-        <is>
-          <t>MNQ Short at 10/01 10:06 — 0 min after a loss, size 2</t>
-        </is>
-      </c>
-    </row>
-    <row r="71">
-      <c r="A71" t="inlineStr">
-        <is>
-          <t>Possible revenge trade</t>
-        </is>
-      </c>
-      <c r="B71" t="inlineStr">
-        <is>
-          <t>MNQ Short at 10/01 10:10 — 4 min after a loss, size 2</t>
-        </is>
-      </c>
-    </row>
-    <row r="72">
-      <c r="A72" t="inlineStr">
-        <is>
-          <t>Possible revenge trade</t>
-        </is>
-      </c>
-      <c r="B72" t="inlineStr">
-        <is>
-          <t>MNQ Long at 10/02 10:29 — 7 min after a loss, size 3</t>
-        </is>
-      </c>
-    </row>
-    <row r="73">
-      <c r="A73" t="inlineStr">
-        <is>
-          <t>Winner cut short</t>
-        </is>
-      </c>
-      <c r="B73" t="inlineStr">
-        <is>
-          <t>MNQ 09/23 11:06 took 0.24R of 0.74R target</t>
-        </is>
-      </c>
-    </row>
-    <row r="74">
-      <c r="A74" t="inlineStr">
-        <is>
-          <t>Winner cut short</t>
-        </is>
-      </c>
-      <c r="B74" t="inlineStr">
-        <is>
-          <t>MNQ 09/30 09:40 took 0.47R of 1.91R target</t>
-        </is>
-      </c>
-    </row>
-    <row r="75">
-      <c r="A75" t="inlineStr">
-        <is>
-          <t>Negative-edge setup</t>
-        </is>
-      </c>
-      <c r="B75" t="inlineStr">
-        <is>
-          <t>Break and Retest: 61 trades, 61% win, $-512 total</t>
-        </is>
-      </c>
-    </row>
-    <row r="76">
-      <c r="A76" t="inlineStr">
-        <is>
-          <t>Negative-edge instrument</t>
-        </is>
-      </c>
-      <c r="B76" t="inlineStr">
-        <is>
-          <t>MYM: 11 trades, 45% win, $-104 total</t>
-        </is>
-      </c>
-    </row>
-    <row r="77">
-      <c r="A77" t="inlineStr">
-        <is>
-          <t>Negative-edge instrument</t>
-        </is>
-      </c>
-      <c r="B77" t="inlineStr">
-        <is>
-          <t>MES: 11 trades, 55% win, $-184 total</t>
-        </is>
-      </c>
-    </row>
-    <row r="78">
-      <c r="A78" t="inlineStr">
-        <is>
-          <t>Negative-edge instrument</t>
-        </is>
-      </c>
-      <c r="B78" t="inlineStr">
-        <is>
-          <t>MGC: 14 trades, 71% win, $-1043 total</t>
-        </is>
-      </c>
-    </row>
-    <row r="79">
-      <c r="A79" t="inlineStr">
-        <is>
-          <t>Negative-edge hour</t>
-        </is>
-      </c>
-      <c r="B79" t="inlineStr">
-        <is>
-          <t>09:00: 9 trades, 44% win, $-11 total</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:A105"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="120" customWidth="1" min="1" max="1"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="25" t="inlineStr">
-        <is>
-          <t>Claude AI Coaching</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="14" t="inlineStr">
-        <is>
-          <t># Trading Journal Review — Critical Coaching</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="14" t="inlineStr"/>
-    </row>
-    <row r="5">
-      <c r="A5" s="14" t="inlineStr">
-        <is>
-          <t>You have a **profitable setup buried under unprofitable execution**. Your 61% win rate should be making money, but you're down $512 because losses are 1.8× your wins and you're not honoring your targeted 1.32 R:R.</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="14" t="inlineStr"/>
-    </row>
-    <row r="7">
-      <c r="A7" s="14" t="inlineStr">
-        <is>
-          <t>## The Core Problem: Massive Execution Gap</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="14" t="inlineStr"/>
-    </row>
-    <row r="9">
-      <c r="A9" s="14" t="inlineStr">
-        <is>
-          <t>| Metric | Target | Actual | Status |</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="14" t="inlineStr">
-        <is>
-          <t>|--------|--------|--------|--------|</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="14" t="inlineStr">
-        <is>
-          <t>| Win Rate | — | 61% | ✓ Good |</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="14" t="inlineStr">
-        <is>
-          <t>| Risk:Reward | 1.32:1 | 0.25:1 | **✗ Critical** |</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="14" t="inlineStr">
-        <is>
-          <t>| Avg Win | — | +$73 | Weak |</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="14" t="inlineStr">
-        <is>
-          <t>| Avg Loss | — | -$134 | Too large |</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="14" t="inlineStr">
-        <is>
-          <t>| Profit Factor | &gt;1.0 | 0.84 | **✗ Losing** |</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="14" t="inlineStr"/>
-    </row>
-    <row r="17">
-      <c r="A17" s="14" t="inlineStr">
-        <is>
-          <t>**You're targeting 1.32 R:R but getting only 0.25.** Either your stops are too wide, your exits are too early, or your position sizing is wrong. Find which one and fix it—this one change could flip you profitable immediately.</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="14" t="inlineStr"/>
-    </row>
-    <row r="19">
-      <c r="A19" s="14" t="inlineStr">
-        <is>
-          <t>---</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="14" t="inlineStr"/>
-    </row>
-    <row r="21">
-      <c r="A21" s="14" t="inlineStr">
-        <is>
-          <t>## Red Flags (Ranked by Severity)</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="14" t="inlineStr"/>
-    </row>
-    <row r="23">
-      <c r="A23" s="14" t="inlineStr">
-        <is>
-          <t>### 1. **Overtrading Destroying Discipline** (Severity: CRITICAL)</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="14" t="inlineStr">
-        <is>
-          <t>- **50 of 61 trades (82%)** flagged as "overtraded"</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="14" t="inlineStr">
-        <is>
-          <t>- Days with 7–12 trades: Sep 23 (9), Sep 24 (11), Sep 25 (7), Sep 29 (11), Oct 1 (12)</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="14" t="inlineStr">
-        <is>
-          <t>- **Action:** Set a hard daily limit of 3–4 trades maximum. Stop when hit. Overtrading = decision fatigue = emotional trade selection.</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="14" t="inlineStr"/>
-    </row>
-    <row r="28">
-      <c r="A28" s="14" t="inlineStr">
-        <is>
-          <t>### 2. **Revenge Trading Pattern** (Severity: CRITICAL)</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" s="14" t="inlineStr">
-        <is>
-          <t>- 19 revenge trades detected, **0–15 min after losses**</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" s="14" t="inlineStr">
-        <is>
-          <t>- These have only **50% win rate** (vs. your 61% overall)</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" s="14" t="inlineStr">
-        <is>
-          <t>- Example: MNQ Short at 10/01 10:06, then another at 10:06 (0 min later), then another at 10:10</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" s="14" t="inlineStr">
-        <is>
-          <t>- **Action:** After a loss, mandatory 30-minute wait before next trade. After 2 consecutive losses, stop for the day.</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" s="14" t="inlineStr"/>
-    </row>
-    <row r="34">
-      <c r="A34" s="14" t="inlineStr">
-        <is>
-          <t>### 3. **Shorts Work, Longs Don't** (Severity: HIGH)</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" s="14" t="inlineStr">
-        <is>
-          <t>| Direction | Trades | Win % | P&amp;L | Expectancy |</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" s="14" t="inlineStr">
-        <is>
-          <t>|-----------|--------|-------|-----|------------|</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" s="14" t="inlineStr">
-        <is>
-          <t>| **Shorts** | 34 | 62% | **+$747** | +$22/trade |</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" s="14" t="inlineStr">
-        <is>
-          <t>| **Longs** | 27 | 59% | **-$1,259** | -$47/trade |</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" s="14" t="inlineStr"/>
-    </row>
-    <row r="40">
-      <c r="A40" s="14" t="inlineStr">
-        <is>
-          <t>You're profitable on shorts and losing badly on longs. **Either your long setup is weaker, or you're chasing longs after failed shorts (tilt).** Audit your long entries—are they on the same quality triggers as shorts?</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" s="14" t="inlineStr"/>
-    </row>
-    <row r="42">
-      <c r="A42" s="14" t="inlineStr">
-        <is>
-          <t>### 4. **MGC Is a Money Pit** (Severity: HIGH)</t>
-        </is>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" s="14" t="inlineStr">
-        <is>
-          <t>- 14 trades, **71% win rate** but **-$1,043 P&amp;L**</t>
-        </is>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" s="14" t="inlineStr">
-        <is>
-          <t>- That's 10 wins for only $73 avg profit, but losses are massive</t>
-        </is>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" s="14" t="inlineStr">
-        <is>
-          <t>- **Action:** Stop trading MGC until you prove profitability. Your position sizing or entry/exit logic is broken for this instrument.</t>
-        </is>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" s="14" t="inlineStr"/>
-    </row>
-    <row r="47">
-      <c r="A47" s="14" t="inlineStr">
-        <is>
-          <t>### 5. **Weak Hour (09:00) + Overnight Suicide Run** (Severity: HIGH)</t>
-        </is>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" s="14" t="inlineStr">
-        <is>
-          <t>- 09:00 AM: 9 trades, 44% win, -$11 (choppy, low-quality)</t>
-        </is>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" s="14" t="inlineStr">
-        <is>
-          <t>- **23:00 PM: 2 trades, 50% win, -$1,304** ← One of your big losses</t>
-        </is>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" s="14" t="inlineStr">
-        <is>
-          <t>- **Action:** Trade only 10:00–14:00 (your sweet spot: +$735 profit in those hours). Avoid 09:00 and never trade overnight.</t>
-        </is>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" s="14" t="inlineStr"/>
-    </row>
-    <row r="52">
-      <c r="A52" s="14" t="inlineStr">
-        <is>
-          <t>### 6. **Winners Being Cut Short** (Severity: MEDIUM)</t>
-        </is>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" s="14" t="inlineStr">
-        <is>
-          <t>- MNQ on 09/23 11:06: took 0.24R of 0.74R target (32% of intended profit)</t>
-        </is>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" s="14" t="inlineStr">
-        <is>
-          <t>- MNQ on 09/30 09:40: took 0.47R of 1.91R target (24% of intended profit)</t>
-        </is>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" s="14" t="inlineStr">
-        <is>
-          <t>- **Action:** Let winners run to target. Don't exit early on winners unless there's a reversal signal.</t>
-        </is>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56" s="14" t="inlineStr"/>
-    </row>
-    <row r="57">
-      <c r="A57" s="14" t="inlineStr">
-        <is>
-          <t>---</t>
-        </is>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58" s="14" t="inlineStr"/>
-    </row>
-    <row r="59">
-      <c r="A59" s="14" t="inlineStr">
-        <is>
-          <t>## What's Working (Build on This)</t>
-        </is>
-      </c>
-    </row>
-    <row r="60">
-      <c r="A60" s="14" t="inlineStr"/>
-    </row>
-    <row r="61">
-      <c r="A61" s="14" t="inlineStr">
-        <is>
-          <t>You have clear **positive indicators**—use them as entry checklist filters:</t>
-        </is>
-      </c>
-    </row>
-    <row r="62">
-      <c r="A62" s="14" t="inlineStr"/>
-    </row>
-    <row r="63">
-      <c r="A63" s="14" t="inlineStr">
-        <is>
-          <t>| Setup | Trades | Win % | P&amp;L | Note |</t>
-        </is>
-      </c>
-    </row>
-    <row r="64">
-      <c r="A64" s="14" t="inlineStr">
-        <is>
-          <t>|-------|--------|-------|-----|------|</t>
-        </is>
-      </c>
-    </row>
-    <row r="65">
-      <c r="A65" s="14" t="inlineStr">
-        <is>
-          <t>| High RVOL (≥1.5x) | 17 | 76% | +$790 | Strong |</t>
-        </is>
-      </c>
-    </row>
-    <row r="66">
-      <c r="A66" s="14" t="inlineStr">
-        <is>
-          <t>| High trigger volume (≥1.2x) | 28 | 67% | +$1,069 | Strongest |</t>
-        </is>
-      </c>
-    </row>
-    <row r="67">
-      <c r="A67" s="14" t="inlineStr">
-        <is>
-          <t>| All 3 Supertrends aligned | 28 | 67% | +$689 | Reliable |</t>
-        </is>
-      </c>
-    </row>
-    <row r="68">
-      <c r="A68" s="14" t="inlineStr">
-        <is>
-          <t>| 5m EMA9/21 cross WITH trade | 40 | 65% | +$708 | Solid |</t>
-        </is>
-      </c>
-    </row>
-    <row r="69">
-      <c r="A69" s="14" t="inlineStr">
-        <is>
-          <t>| Entered at key level | 43 | 62% | +$731 | Solid |</t>
-        </is>
-      </c>
-    </row>
-    <row r="70">
-      <c r="A70" s="14" t="inlineStr">
-        <is>
-          <t>| 5m RSI oversold (≤30) | 4 | 100% | +$342 | Small sample but perfect |</t>
-        </is>
-      </c>
-    </row>
-    <row r="71">
-      <c r="A71" s="14" t="inlineStr"/>
-    </row>
-    <row r="72">
-      <c r="A72" s="14" t="inlineStr">
-        <is>
-          <t>**New rule:** Only enter if **at least 2–3 of these are true**. This will cut your trade count AND improve quality.</t>
-        </is>
-      </c>
-    </row>
-    <row r="73">
-      <c r="A73" s="14" t="inlineStr"/>
-    </row>
-    <row r="74">
-      <c r="A74" s="14" t="inlineStr">
-        <is>
-          <t>---</t>
-        </is>
-      </c>
-    </row>
-    <row r="75">
-      <c r="A75" s="14" t="inlineStr"/>
-    </row>
-    <row r="76">
-      <c r="A76" s="14" t="inlineStr">
-        <is>
-          <t>## Instrument Analysis</t>
-        </is>
-      </c>
-    </row>
-    <row r="77">
-      <c r="A77" s="14" t="inlineStr"/>
-    </row>
-    <row r="78">
-      <c r="A78" s="14" t="inlineStr">
-        <is>
-          <t>| Instrument | Trades | Win % | P&amp;L | Status |</t>
-        </is>
-      </c>
-    </row>
-    <row r="79">
-      <c r="A79" s="14" t="inlineStr">
-        <is>
-          <t>|------------|--------|-------|-----|--------|</t>
-        </is>
-      </c>
-    </row>
-    <row r="80">
-      <c r="A80" s="14" t="inlineStr">
-        <is>
-          <t>| **MNQ** | 25 | 64% | **+$819** | ✓ Trade this |</t>
-        </is>
-      </c>
-    </row>
-    <row r="81">
-      <c r="A81" s="14" t="inlineStr">
-        <is>
-          <t>| MYM | 11 | 45% | -$104 | ✗ Stop or fix |</t>
-        </is>
-      </c>
-    </row>
-    <row r="82">
-      <c r="A82" s="14" t="inlineStr">
-        <is>
-          <t>| MES | 11 | 55% | -$184 | ✗ Stop or fix |</t>
-        </is>
-      </c>
-    </row>
-    <row r="83">
-      <c r="A83" s="14" t="inlineStr">
-        <is>
-          <t>| MGC | 14 | 71% | **-$1,043** | ✗ Stop immediately |</t>
-        </is>
-      </c>
-    </row>
-    <row r="84">
-      <c r="A84" s="14" t="inlineStr"/>
-    </row>
-    <row r="85">
-      <c r="A85" s="14" t="inlineStr">
-        <is>
-          <t>**Action:** Focus 90% of capital on MNQ. Pause MYM, MES, MGC until you prove profitability in those (separate study sessions, not live money).</t>
-        </is>
-      </c>
-    </row>
-    <row r="86">
-      <c r="A86" s="14" t="inlineStr"/>
-    </row>
-    <row r="87">
-      <c r="A87" s="14" t="inlineStr">
-        <is>
-          <t>---</t>
-        </is>
-      </c>
-    </row>
-    <row r="88">
-      <c r="A88" s="14" t="inlineStr"/>
-    </row>
-    <row r="89">
-      <c r="A89" s="14" t="inlineStr">
-        <is>
-          <t>## Immediate Action Plan</t>
-        </is>
-      </c>
-    </row>
-    <row r="90">
-      <c r="A90" s="14" t="inlineStr"/>
-    </row>
-    <row r="91">
-      <c r="A91" s="14" t="inlineStr">
-        <is>
-          <t>**This week:**</t>
-        </is>
-      </c>
-    </row>
-    <row r="92">
-      <c r="A92" s="14" t="inlineStr">
-        <is>
-          <t>1. Set daily trade limit to **3–4 trades max**, stop when hit</t>
-        </is>
-      </c>
-    </row>
-    <row r="93">
-      <c r="A93" s="14" t="inlineStr">
-        <is>
-          <t>2. After a loss, wait **30 min** before next trade</t>
-        </is>
-      </c>
-    </row>
-    <row r="94">
-      <c r="A94" s="14" t="inlineStr">
-        <is>
-          <t>3. Trade **only 10:00–14:00** window</t>
-        </is>
-      </c>
-    </row>
-    <row r="95">
-      <c r="A95" s="14" t="inlineStr">
-        <is>
-          <t>4. Require **2+ positive indicators aligned** before entry</t>
-        </is>
-      </c>
-    </row>
-    <row r="96">
-      <c r="A96" s="14" t="inlineStr">
-        <is>
-          <t>5. Stop trading **MGC immediately**</t>
-        </is>
-      </c>
-    </row>
-    <row r="97">
-      <c r="A97" s="14" t="inlineStr">
-        <is>
-          <t>6. Focus **80%+ of capital on MNQ**</t>
-        </is>
-      </c>
-    </row>
-    <row r="98">
-      <c r="A98" s="14" t="inlineStr">
-        <is>
-          <t>7. Audit your long entry logic vs. shorts — find the gap</t>
-        </is>
-      </c>
-    </row>
-    <row r="99">
-      <c r="A99" s="14" t="inlineStr"/>
-    </row>
-    <row r="100">
-      <c r="A100" s="14" t="inlineStr">
-        <is>
-          <t>**Expected impact:** If you just cut overtrading and add the indicator filter, you should see:</t>
-        </is>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101" s="14" t="inlineStr">
-        <is>
-          <t>- Fewer trades (30–40 vs. 61)</t>
-        </is>
-      </c>
-    </row>
-    <row r="102">
-      <c r="A102" s="14" t="inlineStr">
-        <is>
-          <t>- Higher quality entries (70%+ win rate on filtered setups)</t>
-        </is>
-      </c>
-    </row>
-    <row r="103">
-      <c r="A103" s="14" t="inlineStr">
-        <is>
-          <t>- Better R:R management (closer to your 1.32 target)</t>
-        </is>
-      </c>
-    </row>
-    <row r="104">
-      <c r="A104" s="14" t="inlineStr"/>
-    </row>
-    <row r="105">
-      <c r="A105" s="14" t="inlineStr">
-        <is>
-          <t>Your setup is sound. Your execution discipline is the problem. Fix the process, not the strategy.</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:H5"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="12" customWidth="1" min="1" max="1"/>
-    <col width="10" customWidth="1" min="2" max="2"/>
-    <col width="9" customWidth="1" min="3" max="3"/>
-    <col width="8" customWidth="1" min="4" max="4"/>
-    <col width="34" customWidth="1" min="5" max="5"/>
-    <col width="10" customWidth="1" min="6" max="6"/>
-    <col width="10" customWidth="1" min="7" max="7"/>
-    <col width="10" customWidth="1" min="8" max="8"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="24" t="inlineStr">
-        <is>
-          <t>Date</t>
-        </is>
-      </c>
-      <c r="B1" s="24" t="inlineStr">
-        <is>
-          <t>Time (ET)</t>
-        </is>
-      </c>
-      <c r="C1" s="24" t="inlineStr">
-        <is>
-          <t>Currency</t>
-        </is>
-      </c>
-      <c r="D1" s="24" t="inlineStr">
-        <is>
-          <t>Impact</t>
-        </is>
-      </c>
-      <c r="E1" s="24" t="inlineStr">
-        <is>
-          <t>Event</t>
-        </is>
-      </c>
-      <c r="F1" s="24" t="inlineStr">
-        <is>
-          <t>Actual</t>
-        </is>
-      </c>
-      <c r="G1" s="24" t="inlineStr">
-        <is>
-          <t>Forecast</t>
-        </is>
-      </c>
-      <c r="H1" s="24" t="inlineStr">
-        <is>
-          <t>Previous</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>2026-10-01</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>08:15</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>USD</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>Payrolls</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>90K</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>73K</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>36K</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>2026-10-01</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>08:30</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>USD</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>PCE</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>0.2%</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>0.3%</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>0.1%</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>2026-10-01</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>08:30</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>USD</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>GDP</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>2.2%</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>1.5%</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>2.1%</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>2026-10-02</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>10:00</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>USD</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>ISM</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>52.7</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>52.0</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>51.2</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:AB62"/>
+  <dimension ref="A1:AB77"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -36959,7 +35772,7 @@
         </is>
       </c>
       <c r="J2" t="n">
-        <v>16</v>
+        <v>16.1</v>
       </c>
       <c r="K2" t="inlineStr">
         <is>
@@ -36978,7 +35791,7 @@
         <v>36.67</v>
       </c>
       <c r="O2" t="n">
-        <v>30866.76</v>
+        <v>30866.81</v>
       </c>
       <c r="P2" t="inlineStr">
         <is>
@@ -36992,7 +35805,7 @@
         <v>1.74</v>
       </c>
       <c r="S2" t="n">
-        <v>-60525</v>
+        <v>-59541</v>
       </c>
       <c r="T2" t="n">
         <v>11</v>
@@ -37098,7 +35911,7 @@
         <v>7.46</v>
       </c>
       <c r="O3" t="n">
-        <v>4326.26</v>
+        <v>4326.22</v>
       </c>
       <c r="P3" t="inlineStr">
         <is>
@@ -37109,10 +35922,10 @@
         <v>4323.9</v>
       </c>
       <c r="R3" t="n">
-        <v>1</v>
+        <v>1.03</v>
       </c>
       <c r="S3" t="n">
-        <v>-4405</v>
+        <v>-4290</v>
       </c>
       <c r="T3" t="n">
         <v>4</v>
@@ -37199,7 +36012,7 @@
         </is>
       </c>
       <c r="J4" t="n">
-        <v>45</v>
+        <v>44.9</v>
       </c>
       <c r="K4" t="inlineStr">
         <is>
@@ -37218,7 +36031,7 @@
         <v>7.69</v>
       </c>
       <c r="O4" t="n">
-        <v>4325.41</v>
+        <v>4325.38</v>
       </c>
       <c r="P4" t="inlineStr">
         <is>
@@ -37229,10 +36042,10 @@
         <v>4323.53</v>
       </c>
       <c r="R4" t="n">
-        <v>1.55</v>
+        <v>1.59</v>
       </c>
       <c r="S4" t="n">
-        <v>-3343</v>
+        <v>-3228</v>
       </c>
       <c r="T4" t="n">
         <v>33</v>
@@ -37257,7 +36070,7 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>bullish engulfing</t>
+          <t>strong bullish close</t>
         </is>
       </c>
       <c r="Z4" t="n">
@@ -37338,7 +36151,7 @@
         <v>43.64</v>
       </c>
       <c r="O5" t="n">
-        <v>30802.54</v>
+        <v>30802.55</v>
       </c>
       <c r="P5" t="inlineStr">
         <is>
@@ -37349,10 +36162,10 @@
         <v>30971.35</v>
       </c>
       <c r="R5" t="n">
-        <v>1.31</v>
+        <v>1.18</v>
       </c>
       <c r="S5" t="n">
-        <v>-65104</v>
+        <v>-64289</v>
       </c>
       <c r="T5" t="n">
         <v>15</v>
@@ -37439,7 +36252,7 @@
         </is>
       </c>
       <c r="J6" t="n">
-        <v>47.2</v>
+        <v>47.4</v>
       </c>
       <c r="K6" t="inlineStr">
         <is>
@@ -37469,10 +36282,10 @@
         <v>30804.73</v>
       </c>
       <c r="R6" t="n">
-        <v>0.75</v>
+        <v>0.78</v>
       </c>
       <c r="S6" t="n">
-        <v>-43802</v>
+        <v>-42604</v>
       </c>
       <c r="T6" t="n">
         <v>35</v>
@@ -37495,7 +36308,6 @@
           <t>Round</t>
         </is>
       </c>
-      <c r="Y6" t="inlineStr"/>
       <c r="Z6" t="n">
         <v>0.37</v>
       </c>
@@ -37555,7 +36367,7 @@
         </is>
       </c>
       <c r="J7" t="n">
-        <v>43.2</v>
+        <v>43.3</v>
       </c>
       <c r="K7" t="inlineStr">
         <is>
@@ -37574,7 +36386,7 @@
         <v>42.73</v>
       </c>
       <c r="O7" t="n">
-        <v>30795.72</v>
+        <v>30795.71</v>
       </c>
       <c r="P7" t="inlineStr">
         <is>
@@ -37585,10 +36397,10 @@
         <v>30804.73</v>
       </c>
       <c r="R7" t="n">
-        <v>1.25</v>
+        <v>1.11</v>
       </c>
       <c r="S7" t="n">
-        <v>-45830</v>
+        <v>-44860</v>
       </c>
       <c r="T7" t="n">
         <v>34</v>
@@ -37694,7 +36506,7 @@
         <v>5.45</v>
       </c>
       <c r="O8" t="n">
-        <v>4323.91</v>
+        <v>4323.9</v>
       </c>
       <c r="P8" t="inlineStr">
         <is>
@@ -37705,10 +36517,10 @@
         <v>4323.72</v>
       </c>
       <c r="R8" t="n">
-        <v>1.55</v>
+        <v>1.45</v>
       </c>
       <c r="S8" t="n">
-        <v>-1829</v>
+        <v>-1753</v>
       </c>
       <c r="T8" t="n">
         <v>17</v>
@@ -37737,7 +36549,7 @@
         </is>
       </c>
       <c r="Z8" t="n">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
@@ -37795,7 +36607,7 @@
         </is>
       </c>
       <c r="J9" t="n">
-        <v>35.1</v>
+        <v>35</v>
       </c>
       <c r="K9" t="inlineStr">
         <is>
@@ -37814,7 +36626,7 @@
         <v>32.08</v>
       </c>
       <c r="O9" t="n">
-        <v>30775.83</v>
+        <v>30775.82</v>
       </c>
       <c r="P9" t="inlineStr">
         <is>
@@ -37825,10 +36637,10 @@
         <v>30739.94</v>
       </c>
       <c r="R9" t="n">
-        <v>1.46</v>
+        <v>1.36</v>
       </c>
       <c r="S9" t="n">
-        <v>-58182</v>
+        <v>-57224</v>
       </c>
       <c r="T9" t="n">
         <v>13</v>
@@ -37931,10 +36743,10 @@
         <v>25.8</v>
       </c>
       <c r="N10" t="n">
-        <v>35.07</v>
+        <v>35.06</v>
       </c>
       <c r="O10" t="n">
-        <v>30770.1</v>
+        <v>30770.09</v>
       </c>
       <c r="P10" t="inlineStr">
         <is>
@@ -37945,10 +36757,10 @@
         <v>30739.94</v>
       </c>
       <c r="R10" t="n">
-        <v>2.77</v>
+        <v>2.76</v>
       </c>
       <c r="S10" t="n">
-        <v>-50596</v>
+        <v>-49639</v>
       </c>
       <c r="T10" t="n">
         <v>27</v>
@@ -38054,7 +36866,7 @@
         <v>58.42</v>
       </c>
       <c r="O11" t="n">
-        <v>51721.75</v>
+        <v>51721.6</v>
       </c>
       <c r="P11" t="inlineStr">
         <is>
@@ -38065,10 +36877,10 @@
         <v>51777.56</v>
       </c>
       <c r="R11" t="n">
-        <v>0.75</v>
+        <v>0.7</v>
       </c>
       <c r="S11" t="n">
-        <v>497</v>
+        <v>564</v>
       </c>
       <c r="T11" t="n">
         <v>42</v>
@@ -38155,7 +36967,7 @@
         </is>
       </c>
       <c r="J12" t="n">
-        <v>59.3</v>
+        <v>59.4</v>
       </c>
       <c r="K12" t="inlineStr">
         <is>
@@ -38174,7 +36986,7 @@
         <v>5.72</v>
       </c>
       <c r="O12" t="n">
-        <v>7740.66</v>
+        <v>7740.65</v>
       </c>
       <c r="P12" t="inlineStr">
         <is>
@@ -38188,7 +37000,7 @@
         <v>0.66</v>
       </c>
       <c r="S12" t="n">
-        <v>37751</v>
+        <v>36067</v>
       </c>
       <c r="T12" t="n">
         <v>69</v>
@@ -38211,7 +37023,6 @@
           <t>No</t>
         </is>
       </c>
-      <c r="Y12" t="inlineStr"/>
       <c r="Z12" t="n">
         <v>1.85</v>
       </c>
@@ -38271,7 +37082,7 @@
         </is>
       </c>
       <c r="J13" t="n">
-        <v>54.2</v>
+        <v>54.4</v>
       </c>
       <c r="K13" t="inlineStr">
         <is>
@@ -38290,7 +37101,7 @@
         <v>58.86</v>
       </c>
       <c r="O13" t="n">
-        <v>51721.62</v>
+        <v>51721.53</v>
       </c>
       <c r="P13" t="inlineStr">
         <is>
@@ -38301,10 +37112,10 @@
         <v>51777.56</v>
       </c>
       <c r="R13" t="n">
-        <v>0.73</v>
+        <v>0.72</v>
       </c>
       <c r="S13" t="n">
-        <v>1579</v>
+        <v>1703</v>
       </c>
       <c r="T13" t="n">
         <v>38</v>
@@ -38391,7 +37202,7 @@
         </is>
       </c>
       <c r="J14" t="n">
-        <v>68.09999999999999</v>
+        <v>68.3</v>
       </c>
       <c r="K14" t="inlineStr">
         <is>
@@ -38410,7 +37221,7 @@
         <v>5.97</v>
       </c>
       <c r="O14" t="n">
-        <v>7742.53</v>
+        <v>7742.51</v>
       </c>
       <c r="P14" t="inlineStr">
         <is>
@@ -38421,10 +37232,10 @@
         <v>7736.23</v>
       </c>
       <c r="R14" t="n">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="S14" t="n">
-        <v>64281</v>
+        <v>63449</v>
       </c>
       <c r="T14" t="n">
         <v>2</v>
@@ -38511,7 +37322,7 @@
         </is>
       </c>
       <c r="J15" t="n">
-        <v>45.8</v>
+        <v>45.7</v>
       </c>
       <c r="K15" t="inlineStr">
         <is>
@@ -38530,7 +37341,7 @@
         <v>55.16</v>
       </c>
       <c r="O15" t="n">
-        <v>51725.5</v>
+        <v>51725.41</v>
       </c>
       <c r="P15" t="inlineStr">
         <is>
@@ -38541,10 +37352,10 @@
         <v>51777.56</v>
       </c>
       <c r="R15" t="n">
-        <v>0.51</v>
+        <v>0.49</v>
       </c>
       <c r="S15" t="n">
-        <v>-317</v>
+        <v>-195</v>
       </c>
       <c r="T15" t="n">
         <v>52</v>
@@ -38567,7 +37378,6 @@
           <t>Round</t>
         </is>
       </c>
-      <c r="Y15" t="inlineStr"/>
       <c r="Z15" t="n">
         <v>0.5600000000000001</v>
       </c>
@@ -38627,7 +37437,7 @@
         </is>
       </c>
       <c r="J16" t="n">
-        <v>44.7</v>
+        <v>44.6</v>
       </c>
       <c r="K16" t="inlineStr">
         <is>
@@ -38646,7 +37456,7 @@
         <v>54.58</v>
       </c>
       <c r="O16" t="n">
-        <v>51723.58</v>
+        <v>51723.49</v>
       </c>
       <c r="P16" t="inlineStr">
         <is>
@@ -38657,10 +37467,10 @@
         <v>51777.56</v>
       </c>
       <c r="R16" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.75</v>
       </c>
       <c r="S16" t="n">
-        <v>-20</v>
+        <v>70</v>
       </c>
       <c r="T16" t="n">
         <v>25</v>
@@ -38747,7 +37557,7 @@
         </is>
       </c>
       <c r="J17" t="n">
-        <v>35.7</v>
+        <v>35.6</v>
       </c>
       <c r="K17" t="inlineStr">
         <is>
@@ -38763,10 +37573,10 @@
         <v>20.2</v>
       </c>
       <c r="N17" t="n">
-        <v>5.62</v>
+        <v>5.61</v>
       </c>
       <c r="O17" t="n">
-        <v>4302.28</v>
+        <v>4302.26</v>
       </c>
       <c r="P17" t="inlineStr">
         <is>
@@ -38780,7 +37590,7 @@
         <v>0.58</v>
       </c>
       <c r="S17" t="n">
-        <v>-1357</v>
+        <v>-1642</v>
       </c>
       <c r="T17" t="n">
         <v>67</v>
@@ -38867,7 +37677,7 @@
         </is>
       </c>
       <c r="J18" t="n">
-        <v>30.8</v>
+        <v>30.9</v>
       </c>
       <c r="K18" t="inlineStr">
         <is>
@@ -38886,7 +37696,7 @@
         <v>5.63</v>
       </c>
       <c r="O18" t="n">
-        <v>4300.35</v>
+        <v>4300.34</v>
       </c>
       <c r="P18" t="inlineStr">
         <is>
@@ -38900,7 +37710,7 @@
         <v>1.02</v>
       </c>
       <c r="S18" t="n">
-        <v>-3190</v>
+        <v>-3331</v>
       </c>
       <c r="T18" t="n">
         <v>10</v>
@@ -38987,7 +37797,7 @@
         </is>
       </c>
       <c r="J19" t="n">
-        <v>41.2</v>
+        <v>41.1</v>
       </c>
       <c r="K19" t="inlineStr">
         <is>
@@ -39003,10 +37813,10 @@
         <v>23.4</v>
       </c>
       <c r="N19" t="n">
-        <v>37.75</v>
+        <v>37.76</v>
       </c>
       <c r="O19" t="n">
-        <v>30572.55</v>
+        <v>30572.56</v>
       </c>
       <c r="P19" t="inlineStr">
         <is>
@@ -39017,10 +37827,10 @@
         <v>30520.72</v>
       </c>
       <c r="R19" t="n">
-        <v>1.19</v>
+        <v>1.2</v>
       </c>
       <c r="S19" t="n">
-        <v>14350</v>
+        <v>15374</v>
       </c>
       <c r="T19" t="n">
         <v>12</v>
@@ -39049,7 +37859,7 @@
         </is>
       </c>
       <c r="Z19" t="n">
-        <v>0.71</v>
+        <v>0.72</v>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
@@ -39126,7 +37936,7 @@
         <v>57.79</v>
       </c>
       <c r="O20" t="n">
-        <v>51679.05</v>
+        <v>51678.83</v>
       </c>
       <c r="P20" t="inlineStr">
         <is>
@@ -39140,7 +37950,7 @@
         <v>1.6</v>
       </c>
       <c r="S20" t="n">
-        <v>383</v>
+        <v>380</v>
       </c>
       <c r="T20" t="n">
         <v>30</v>
@@ -39163,7 +37973,6 @@
           <t>No</t>
         </is>
       </c>
-      <c r="Y20" t="inlineStr"/>
       <c r="Z20" t="n">
         <v>0.77</v>
       </c>
@@ -39223,7 +38032,7 @@
         </is>
       </c>
       <c r="J21" t="n">
-        <v>55.1</v>
+        <v>55.3</v>
       </c>
       <c r="K21" t="inlineStr">
         <is>
@@ -39242,7 +38051,7 @@
         <v>8.91</v>
       </c>
       <c r="O21" t="n">
-        <v>7753.35</v>
+        <v>7753.33</v>
       </c>
       <c r="P21" t="inlineStr">
         <is>
@@ -39256,7 +38065,7 @@
         <v>1.3</v>
       </c>
       <c r="S21" t="n">
-        <v>59161</v>
+        <v>49906</v>
       </c>
       <c r="T21" t="n">
         <v>29</v>
@@ -39279,7 +38088,6 @@
           <t>No</t>
         </is>
       </c>
-      <c r="Y21" t="inlineStr"/>
       <c r="Z21" t="n">
         <v>0.67</v>
       </c>
@@ -39339,7 +38147,7 @@
         </is>
       </c>
       <c r="J22" t="n">
-        <v>47.1</v>
+        <v>47</v>
       </c>
       <c r="K22" t="inlineStr">
         <is>
@@ -39352,10 +38160,10 @@
         </is>
       </c>
       <c r="M22" t="n">
-        <v>27.6</v>
+        <v>27.5</v>
       </c>
       <c r="N22" t="n">
-        <v>5.44</v>
+        <v>5.43</v>
       </c>
       <c r="O22" t="n">
         <v>7783</v>
@@ -39372,7 +38180,7 @@
         <v>0.93</v>
       </c>
       <c r="S22" t="n">
-        <v>49661</v>
+        <v>49652</v>
       </c>
       <c r="T22" t="n">
         <v>55</v>
@@ -39395,7 +38203,6 @@
           <t>PDH</t>
         </is>
       </c>
-      <c r="Y22" t="inlineStr"/>
       <c r="Z22" t="n">
         <v>2.94</v>
       </c>
@@ -39455,7 +38262,7 @@
         </is>
       </c>
       <c r="J23" t="n">
-        <v>56.6</v>
+        <v>56.4</v>
       </c>
       <c r="K23" t="inlineStr">
         <is>
@@ -39471,10 +38278,10 @@
         <v>16.9</v>
       </c>
       <c r="N23" t="n">
-        <v>49.53</v>
+        <v>49.55</v>
       </c>
       <c r="O23" t="n">
-        <v>51869.93</v>
+        <v>51870.14</v>
       </c>
       <c r="P23" t="inlineStr">
         <is>
@@ -39485,10 +38292,10 @@
         <v>51802.57</v>
       </c>
       <c r="R23" t="n">
-        <v>0.75</v>
+        <v>0.71</v>
       </c>
       <c r="S23" t="n">
-        <v>3250</v>
+        <v>3388</v>
       </c>
       <c r="T23" t="n">
         <v>16</v>
@@ -39575,7 +38382,7 @@
         </is>
       </c>
       <c r="J24" t="n">
-        <v>32.2</v>
+        <v>32</v>
       </c>
       <c r="K24" t="inlineStr">
         <is>
@@ -39594,7 +38401,7 @@
         <v>7.3</v>
       </c>
       <c r="O24" t="n">
-        <v>4306.29</v>
+        <v>4306.3</v>
       </c>
       <c r="P24" t="inlineStr">
         <is>
@@ -39605,10 +38412,10 @@
         <v>4302.59</v>
       </c>
       <c r="R24" t="n">
-        <v>0.88</v>
+        <v>0.96</v>
       </c>
       <c r="S24" t="n">
-        <v>1600</v>
+        <v>1438</v>
       </c>
       <c r="T24" t="n">
         <v>50</v>
@@ -39631,9 +38438,13 @@
           <t>No</t>
         </is>
       </c>
-      <c r="Y24" t="inlineStr"/>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>bullish pin/hammer</t>
+        </is>
+      </c>
       <c r="Z24" t="n">
-        <v>0.88</v>
+        <v>0.87</v>
       </c>
       <c r="AA24" t="inlineStr">
         <is>
@@ -39691,7 +38502,7 @@
         </is>
       </c>
       <c r="J25" t="n">
-        <v>38.6</v>
+        <v>38.8</v>
       </c>
       <c r="K25" t="inlineStr">
         <is>
@@ -39710,7 +38521,7 @@
         <v>48.02</v>
       </c>
       <c r="O25" t="n">
-        <v>30810.51</v>
+        <v>30810.52</v>
       </c>
       <c r="P25" t="inlineStr">
         <is>
@@ -39721,10 +38532,10 @@
         <v>30808.28</v>
       </c>
       <c r="R25" t="n">
-        <v>1.13</v>
+        <v>1.16</v>
       </c>
       <c r="S25" t="n">
-        <v>28194</v>
+        <v>28214</v>
       </c>
       <c r="T25" t="n">
         <v>23</v>
@@ -39749,7 +38560,7 @@
       </c>
       <c r="Y25" t="inlineStr">
         <is>
-          <t>bullish engulfing</t>
+          <t>strong bullish close</t>
         </is>
       </c>
       <c r="Z25" t="n">
@@ -39841,10 +38652,10 @@
         <v>30808.28</v>
       </c>
       <c r="R26" t="n">
-        <v>1.07</v>
+        <v>1.09</v>
       </c>
       <c r="S26" t="n">
-        <v>30159</v>
+        <v>29840</v>
       </c>
       <c r="T26" t="n">
         <v>27</v>
@@ -39931,7 +38742,7 @@
         </is>
       </c>
       <c r="J27" t="n">
-        <v>43</v>
+        <v>43.1</v>
       </c>
       <c r="K27" t="inlineStr">
         <is>
@@ -39964,7 +38775,7 @@
         <v>0.85</v>
       </c>
       <c r="S27" t="n">
-        <v>38250</v>
+        <v>38048</v>
       </c>
       <c r="T27" t="n">
         <v>31</v>
@@ -40051,7 +38862,7 @@
         </is>
       </c>
       <c r="J28" t="n">
-        <v>43</v>
+        <v>43.1</v>
       </c>
       <c r="K28" t="inlineStr">
         <is>
@@ -40084,7 +38895,7 @@
         <v>0.85</v>
       </c>
       <c r="S28" t="n">
-        <v>38250</v>
+        <v>38048</v>
       </c>
       <c r="T28" t="n">
         <v>32</v>
@@ -40171,7 +38982,7 @@
         </is>
       </c>
       <c r="J29" t="n">
-        <v>18.1</v>
+        <v>18.2</v>
       </c>
       <c r="K29" t="inlineStr">
         <is>
@@ -40190,7 +39001,7 @@
         <v>5.58</v>
       </c>
       <c r="O29" t="n">
-        <v>4264.59</v>
+        <v>4266.63</v>
       </c>
       <c r="P29" t="inlineStr">
         <is>
@@ -40201,10 +39012,10 @@
         <v>4253.51</v>
       </c>
       <c r="R29" t="n">
-        <v>1.89</v>
+        <v>1.77</v>
       </c>
       <c r="S29" t="n">
-        <v>-2824</v>
+        <v>-4757</v>
       </c>
       <c r="T29" t="n">
         <v>-1</v>
@@ -40310,7 +39121,7 @@
         <v>4.96</v>
       </c>
       <c r="O30" t="n">
-        <v>4258.83</v>
+        <v>4260.8</v>
       </c>
       <c r="P30" t="inlineStr">
         <is>
@@ -40321,10 +39132,10 @@
         <v>4253.09</v>
       </c>
       <c r="R30" t="n">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="S30" t="n">
-        <v>-3420</v>
+        <v>-5373</v>
       </c>
       <c r="T30" t="n">
         <v>185</v>
@@ -40353,7 +39164,7 @@
         </is>
       </c>
       <c r="Z30" t="n">
-        <v>0.63</v>
+        <v>0.64</v>
       </c>
       <c r="AA30" t="inlineStr">
         <is>
@@ -40411,7 +39222,7 @@
         </is>
       </c>
       <c r="J31" t="n">
-        <v>54.8</v>
+        <v>54.7</v>
       </c>
       <c r="K31" t="inlineStr">
         <is>
@@ -40427,7 +39238,7 @@
         <v>7.7</v>
       </c>
       <c r="N31" t="n">
-        <v>4.01</v>
+        <v>4</v>
       </c>
       <c r="O31" t="n">
         <v>4164.38</v>
@@ -40444,7 +39255,7 @@
         <v>1.12</v>
       </c>
       <c r="S31" t="n">
-        <v>-5083</v>
+        <v>-5201</v>
       </c>
       <c r="T31" t="n">
         <v>34</v>
@@ -40467,7 +39278,6 @@
           <t>ORL</t>
         </is>
       </c>
-      <c r="Y31" t="inlineStr"/>
       <c r="Z31" t="n">
         <v>0.76</v>
       </c>
@@ -40527,7 +39337,7 @@
         </is>
       </c>
       <c r="J32" t="n">
-        <v>33.1</v>
+        <v>33.5</v>
       </c>
       <c r="K32" t="inlineStr">
         <is>
@@ -40543,10 +39353,10 @@
         <v>28.2</v>
       </c>
       <c r="N32" t="n">
-        <v>48.29</v>
+        <v>48.19</v>
       </c>
       <c r="O32" t="n">
-        <v>51759.5</v>
+        <v>51759.34</v>
       </c>
       <c r="P32" t="inlineStr">
         <is>
@@ -40557,10 +39367,10 @@
         <v>51745.1</v>
       </c>
       <c r="R32" t="n">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="S32" t="n">
-        <v>-1308</v>
+        <v>-1577</v>
       </c>
       <c r="T32" t="n">
         <v>20</v>
@@ -40583,9 +39393,8 @@
           <t>PDL</t>
         </is>
       </c>
-      <c r="Y32" t="inlineStr"/>
       <c r="Z32" t="n">
-        <v>2.43</v>
+        <v>2.42</v>
       </c>
       <c r="AA32" t="inlineStr">
         <is>
@@ -40643,7 +39452,7 @@
         </is>
       </c>
       <c r="J33" t="n">
-        <v>27</v>
+        <v>27.5</v>
       </c>
       <c r="K33" t="inlineStr">
         <is>
@@ -40659,10 +39468,10 @@
         <v>30.1</v>
       </c>
       <c r="N33" t="n">
-        <v>52.04</v>
+        <v>51.95</v>
       </c>
       <c r="O33" t="n">
-        <v>51751.77</v>
+        <v>51751.45</v>
       </c>
       <c r="P33" t="inlineStr">
         <is>
@@ -40676,7 +39485,7 @@
         <v>0.9</v>
       </c>
       <c r="S33" t="n">
-        <v>-3515</v>
+        <v>-3784</v>
       </c>
       <c r="T33" t="n">
         <v>28</v>
@@ -40696,12 +39505,7 @@
       </c>
       <c r="X33" t="inlineStr">
         <is>
-          <t>PDL</t>
-        </is>
-      </c>
-      <c r="Y33" t="inlineStr">
-        <is>
-          <t>bearish pin</t>
+          <t>No</t>
         </is>
       </c>
       <c r="Z33" t="n">
@@ -40763,7 +39567,7 @@
         </is>
       </c>
       <c r="J34" t="n">
-        <v>62.8</v>
+        <v>63</v>
       </c>
       <c r="K34" t="inlineStr">
         <is>
@@ -40782,7 +39586,7 @@
         <v>5.85</v>
       </c>
       <c r="O34" t="n">
-        <v>4191.64</v>
+        <v>4191.7</v>
       </c>
       <c r="P34" t="inlineStr">
         <is>
@@ -40793,10 +39597,10 @@
         <v>4190.53</v>
       </c>
       <c r="R34" t="n">
-        <v>1</v>
+        <v>1.23</v>
       </c>
       <c r="S34" t="n">
-        <v>431</v>
+        <v>602</v>
       </c>
       <c r="T34" t="n">
         <v>7</v>
@@ -40819,9 +39623,8 @@
           <t>ORH/Round</t>
         </is>
       </c>
-      <c r="Y34" t="inlineStr"/>
       <c r="Z34" t="n">
-        <v>1.76</v>
+        <v>1.77</v>
       </c>
       <c r="AA34" t="inlineStr">
         <is>
@@ -40898,7 +39701,7 @@
         <v>39.62</v>
       </c>
       <c r="O35" t="n">
-        <v>30618.17</v>
+        <v>30618.22</v>
       </c>
       <c r="P35" t="inlineStr">
         <is>
@@ -40912,7 +39715,7 @@
         <v>0.83</v>
       </c>
       <c r="S35" t="n">
-        <v>-19008</v>
+        <v>-18855</v>
       </c>
       <c r="T35" t="n">
         <v>57</v>
@@ -40935,7 +39738,6 @@
           <t>Round</t>
         </is>
       </c>
-      <c r="Y35" t="inlineStr"/>
       <c r="Z35" t="n">
         <v>1.1</v>
       </c>
@@ -41008,13 +39810,13 @@
         </is>
       </c>
       <c r="M36" t="n">
-        <v>34.7</v>
+        <v>34.6</v>
       </c>
       <c r="N36" t="n">
-        <v>6.4</v>
+        <v>6.39</v>
       </c>
       <c r="O36" t="n">
-        <v>7742.66</v>
+        <v>7742.68</v>
       </c>
       <c r="P36" t="inlineStr">
         <is>
@@ -41025,10 +39827,10 @@
         <v>7741.58</v>
       </c>
       <c r="R36" t="n">
-        <v>1.04</v>
+        <v>1</v>
       </c>
       <c r="S36" t="n">
-        <v>-15949</v>
+        <v>-17972</v>
       </c>
       <c r="T36" t="n">
         <v>36</v>
@@ -41115,7 +39917,7 @@
         </is>
       </c>
       <c r="J37" t="n">
-        <v>37.3</v>
+        <v>37.4</v>
       </c>
       <c r="K37" t="inlineStr">
         <is>
@@ -41128,13 +39930,13 @@
         </is>
       </c>
       <c r="M37" t="n">
-        <v>28.2</v>
+        <v>28</v>
       </c>
       <c r="N37" t="n">
-        <v>7.15</v>
+        <v>7.14</v>
       </c>
       <c r="O37" t="n">
-        <v>7740.49</v>
+        <v>7740.5</v>
       </c>
       <c r="P37" t="inlineStr">
         <is>
@@ -41145,13 +39947,11 @@
         <v>7741.07</v>
       </c>
       <c r="R37" t="n">
-        <v>0.91</v>
+        <v>0.97</v>
       </c>
       <c r="S37" t="n">
-        <v>-51651</v>
-      </c>
-      <c r="T37" t="inlineStr"/>
-      <c r="U37" t="inlineStr"/>
+        <v>-55883</v>
+      </c>
       <c r="V37" t="inlineStr">
         <is>
           <t>No setup</t>
@@ -41229,7 +40029,7 @@
         </is>
       </c>
       <c r="J38" t="n">
-        <v>40.6</v>
+        <v>40.9</v>
       </c>
       <c r="K38" t="inlineStr">
         <is>
@@ -41242,13 +40042,13 @@
         </is>
       </c>
       <c r="M38" t="n">
-        <v>32.5</v>
+        <v>32.3</v>
       </c>
       <c r="N38" t="n">
-        <v>7.54</v>
+        <v>7.53</v>
       </c>
       <c r="O38" t="n">
-        <v>7737.1</v>
+        <v>7737.11</v>
       </c>
       <c r="P38" t="inlineStr">
         <is>
@@ -41259,10 +40059,10 @@
         <v>7741.45</v>
       </c>
       <c r="R38" t="n">
-        <v>1.53</v>
+        <v>1.55</v>
       </c>
       <c r="S38" t="n">
-        <v>-50492</v>
+        <v>-53681</v>
       </c>
       <c r="T38" t="n">
         <v>67</v>
@@ -41362,13 +40162,13 @@
         </is>
       </c>
       <c r="M39" t="n">
-        <v>29.3</v>
+        <v>29.1</v>
       </c>
       <c r="N39" t="n">
         <v>7.39</v>
       </c>
       <c r="O39" t="n">
-        <v>7735.98</v>
+        <v>7735.99</v>
       </c>
       <c r="P39" t="inlineStr">
         <is>
@@ -41379,10 +40179,10 @@
         <v>7741.45</v>
       </c>
       <c r="R39" t="n">
-        <v>2.51</v>
+        <v>2.44</v>
       </c>
       <c r="S39" t="n">
-        <v>-42814</v>
+        <v>-46011</v>
       </c>
       <c r="T39" t="n">
         <v>28</v>
@@ -41405,7 +40205,6 @@
           <t>No</t>
         </is>
       </c>
-      <c r="Y39" t="inlineStr"/>
       <c r="Z39" t="n">
         <v>1.86</v>
       </c>
@@ -41465,7 +40264,7 @@
         </is>
       </c>
       <c r="J40" t="n">
-        <v>54</v>
+        <v>54.1</v>
       </c>
       <c r="K40" t="inlineStr">
         <is>
@@ -41484,7 +40283,7 @@
         <v>33.91</v>
       </c>
       <c r="O40" t="n">
-        <v>51635.6</v>
+        <v>51635.5</v>
       </c>
       <c r="P40" t="inlineStr">
         <is>
@@ -41495,10 +40294,10 @@
         <v>51745.89</v>
       </c>
       <c r="R40" t="n">
-        <v>0.9</v>
+        <v>0.87</v>
       </c>
       <c r="S40" t="n">
-        <v>-5366</v>
+        <v>-5582</v>
       </c>
       <c r="T40" t="n">
         <v>8</v>
@@ -41604,7 +40403,7 @@
         <v>33.53</v>
       </c>
       <c r="O41" t="n">
-        <v>51634.34</v>
+        <v>51634.25</v>
       </c>
       <c r="P41" t="inlineStr">
         <is>
@@ -41618,7 +40417,7 @@
         <v>1.87</v>
       </c>
       <c r="S41" t="n">
-        <v>-5368</v>
+        <v>-5584</v>
       </c>
       <c r="T41" t="n">
         <v>8</v>
@@ -41724,7 +40523,7 @@
         <v>33.53</v>
       </c>
       <c r="O42" t="n">
-        <v>51634.34</v>
+        <v>51634.25</v>
       </c>
       <c r="P42" t="inlineStr">
         <is>
@@ -41738,7 +40537,7 @@
         <v>1.87</v>
       </c>
       <c r="S42" t="n">
-        <v>-5368</v>
+        <v>-5584</v>
       </c>
       <c r="T42" t="n">
         <v>19</v>
@@ -41825,7 +40624,7 @@
         </is>
       </c>
       <c r="J43" t="n">
-        <v>64</v>
+        <v>64.09999999999999</v>
       </c>
       <c r="K43" t="inlineStr">
         <is>
@@ -41843,11 +40642,6 @@
       <c r="N43" t="n">
         <v>46.04</v>
       </c>
-      <c r="O43" t="inlineStr"/>
-      <c r="P43" t="inlineStr"/>
-      <c r="Q43" t="inlineStr"/>
-      <c r="R43" t="inlineStr"/>
-      <c r="S43" t="inlineStr"/>
       <c r="T43" t="n">
         <v>28</v>
       </c>
@@ -41869,7 +40663,6 @@
           <t>PDH/Round</t>
         </is>
       </c>
-      <c r="Y43" t="inlineStr"/>
       <c r="Z43" t="n">
         <v>3.46</v>
       </c>
@@ -41948,7 +40741,7 @@
         <v>47.52</v>
       </c>
       <c r="O44" t="n">
-        <v>30747.97</v>
+        <v>30748.14</v>
       </c>
       <c r="P44" t="inlineStr">
         <is>
@@ -41959,10 +40752,10 @@
         <v>30747.96</v>
       </c>
       <c r="R44" t="n">
-        <v>0.86</v>
+        <v>0.89</v>
       </c>
       <c r="S44" t="n">
-        <v>22068</v>
+        <v>22955</v>
       </c>
       <c r="T44" t="n">
         <v>28</v>
@@ -41987,7 +40780,7 @@
       </c>
       <c r="Y44" t="inlineStr">
         <is>
-          <t>strong bullish close</t>
+          <t>bullish engulfing</t>
         </is>
       </c>
       <c r="Z44" t="n">
@@ -42068,7 +40861,7 @@
         <v>7.16</v>
       </c>
       <c r="O45" t="n">
-        <v>4212.49</v>
+        <v>4212.47</v>
       </c>
       <c r="P45" t="inlineStr">
         <is>
@@ -42082,10 +40875,8 @@
         <v>1.08</v>
       </c>
       <c r="S45" t="n">
-        <v>-301</v>
-      </c>
-      <c r="T45" t="inlineStr"/>
-      <c r="U45" t="inlineStr"/>
+        <v>-329</v>
+      </c>
       <c r="V45" t="inlineStr">
         <is>
           <t>No setup</t>
@@ -42099,7 +40890,6 @@
           <t>Round</t>
         </is>
       </c>
-      <c r="Y45" t="inlineStr"/>
       <c r="Z45" t="n">
         <v>0.77</v>
       </c>
@@ -42178,7 +40968,7 @@
         <v>50.47</v>
       </c>
       <c r="O46" t="n">
-        <v>30779.54</v>
+        <v>30779.41</v>
       </c>
       <c r="P46" t="inlineStr">
         <is>
@@ -42189,10 +40979,10 @@
         <v>30795.74</v>
       </c>
       <c r="R46" t="n">
-        <v>1.22</v>
+        <v>1.19</v>
       </c>
       <c r="S46" t="n">
-        <v>1174</v>
+        <v>531</v>
       </c>
       <c r="T46" t="n">
         <v>7</v>
@@ -42279,7 +41069,7 @@
         </is>
       </c>
       <c r="J47" t="n">
-        <v>39.7</v>
+        <v>39.6</v>
       </c>
       <c r="K47" t="inlineStr">
         <is>
@@ -42298,7 +41088,7 @@
         <v>62.68</v>
       </c>
       <c r="O47" t="n">
-        <v>30747.71</v>
+        <v>30747.61</v>
       </c>
       <c r="P47" t="inlineStr">
         <is>
@@ -42309,10 +41099,10 @@
         <v>30792.83</v>
       </c>
       <c r="R47" t="n">
-        <v>2.51</v>
+        <v>2.52</v>
       </c>
       <c r="S47" t="n">
-        <v>-254</v>
+        <v>-1306</v>
       </c>
       <c r="T47" t="n">
         <v>9</v>
@@ -42399,7 +41189,7 @@
         </is>
       </c>
       <c r="J48" t="n">
-        <v>39.7</v>
+        <v>39.6</v>
       </c>
       <c r="K48" t="inlineStr">
         <is>
@@ -42418,7 +41208,7 @@
         <v>62.68</v>
       </c>
       <c r="O48" t="n">
-        <v>30747.71</v>
+        <v>30747.61</v>
       </c>
       <c r="P48" t="inlineStr">
         <is>
@@ -42429,10 +41219,10 @@
         <v>30792.83</v>
       </c>
       <c r="R48" t="n">
-        <v>2.51</v>
+        <v>2.52</v>
       </c>
       <c r="S48" t="n">
-        <v>-254</v>
+        <v>-1306</v>
       </c>
       <c r="T48" t="n">
         <v>7</v>
@@ -42519,7 +41309,7 @@
         </is>
       </c>
       <c r="J49" t="n">
-        <v>35.9</v>
+        <v>35.8</v>
       </c>
       <c r="K49" t="inlineStr">
         <is>
@@ -42538,7 +41328,7 @@
         <v>64.12</v>
       </c>
       <c r="O49" t="n">
-        <v>30741.93</v>
+        <v>30741.87</v>
       </c>
       <c r="P49" t="inlineStr">
         <is>
@@ -42552,7 +41342,7 @@
         <v>1.3</v>
       </c>
       <c r="S49" t="n">
-        <v>-2504</v>
+        <v>-3350</v>
       </c>
       <c r="T49" t="n">
         <v>28</v>
@@ -42575,9 +41365,8 @@
           <t>ONL/ORL/Round</t>
         </is>
       </c>
-      <c r="Y49" t="inlineStr"/>
       <c r="Z49" t="n">
-        <v>1.47</v>
+        <v>1.46</v>
       </c>
       <c r="AA49" t="inlineStr">
         <is>
@@ -42635,7 +41424,7 @@
         </is>
       </c>
       <c r="J50" t="n">
-        <v>31.8</v>
+        <v>31.6</v>
       </c>
       <c r="K50" t="inlineStr">
         <is>
@@ -42654,7 +41443,7 @@
         <v>65.98</v>
       </c>
       <c r="O50" t="n">
-        <v>30724.67</v>
+        <v>30724.56</v>
       </c>
       <c r="P50" t="inlineStr">
         <is>
@@ -42665,10 +41454,10 @@
         <v>30793.26</v>
       </c>
       <c r="R50" t="n">
-        <v>1.81</v>
+        <v>1.8</v>
       </c>
       <c r="S50" t="n">
-        <v>-5196</v>
+        <v>-6367</v>
       </c>
       <c r="T50" t="n">
         <v>17</v>
@@ -42691,7 +41480,6 @@
           <t>Round</t>
         </is>
       </c>
-      <c r="Y50" t="inlineStr"/>
       <c r="Z50" t="n">
         <v>1.46</v>
       </c>
@@ -42770,7 +41558,7 @@
         <v>64.90000000000001</v>
       </c>
       <c r="O51" t="n">
-        <v>30718.16</v>
+        <v>30718.06</v>
       </c>
       <c r="P51" t="inlineStr">
         <is>
@@ -42784,7 +41572,7 @@
         <v>1.49</v>
       </c>
       <c r="S51" t="n">
-        <v>-4937</v>
+        <v>-6107</v>
       </c>
       <c r="T51" t="n">
         <v>18</v>
@@ -42807,7 +41595,6 @@
           <t>Round</t>
         </is>
       </c>
-      <c r="Y51" t="inlineStr"/>
       <c r="Z51" t="n">
         <v>1.15</v>
       </c>
@@ -42867,7 +41654,7 @@
         </is>
       </c>
       <c r="J52" t="n">
-        <v>39.4</v>
+        <v>39.3</v>
       </c>
       <c r="K52" t="inlineStr">
         <is>
@@ -42886,7 +41673,7 @@
         <v>67.23</v>
       </c>
       <c r="O52" t="n">
-        <v>30705.58</v>
+        <v>30705.44</v>
       </c>
       <c r="P52" t="inlineStr">
         <is>
@@ -42897,10 +41684,10 @@
         <v>30793.26</v>
       </c>
       <c r="R52" t="n">
-        <v>1.84</v>
+        <v>1.85</v>
       </c>
       <c r="S52" t="n">
-        <v>1464</v>
+        <v>-248</v>
       </c>
       <c r="T52" t="n">
         <v>49</v>
@@ -42923,9 +41710,8 @@
           <t>Round</t>
         </is>
       </c>
-      <c r="Y52" t="inlineStr"/>
       <c r="Z52" t="n">
-        <v>0.88</v>
+        <v>0.87</v>
       </c>
       <c r="AA52" t="inlineStr">
         <is>
@@ -42983,7 +41769,7 @@
         </is>
       </c>
       <c r="J53" t="n">
-        <v>31.2</v>
+        <v>31.1</v>
       </c>
       <c r="K53" t="inlineStr">
         <is>
@@ -43002,7 +41788,7 @@
         <v>11.5</v>
       </c>
       <c r="O53" t="n">
-        <v>7703.14</v>
+        <v>7703.12</v>
       </c>
       <c r="P53" t="inlineStr">
         <is>
@@ -43016,7 +41802,7 @@
         <v>1.33</v>
       </c>
       <c r="S53" t="n">
-        <v>-86014</v>
+        <v>-91694</v>
       </c>
       <c r="T53" t="n">
         <v>11</v>
@@ -43039,7 +41825,6 @@
           <t>No</t>
         </is>
       </c>
-      <c r="Y53" t="inlineStr"/>
       <c r="Z53" t="n">
         <v>0.79</v>
       </c>
@@ -43118,7 +41903,7 @@
         <v>11.5</v>
       </c>
       <c r="O54" t="n">
-        <v>7701.2</v>
+        <v>7701.18</v>
       </c>
       <c r="P54" t="inlineStr">
         <is>
@@ -43129,10 +41914,10 @@
         <v>7692.08</v>
       </c>
       <c r="R54" t="n">
-        <v>1.42</v>
+        <v>1.34</v>
       </c>
       <c r="S54" t="n">
-        <v>-75856</v>
+        <v>-82725</v>
       </c>
       <c r="T54" t="n">
         <v>25</v>
@@ -43238,7 +42023,7 @@
         <v>12.07</v>
       </c>
       <c r="O55" t="n">
-        <v>7699.76</v>
+        <v>7699.75</v>
       </c>
       <c r="P55" t="inlineStr">
         <is>
@@ -43249,10 +42034,10 @@
         <v>7692.08</v>
       </c>
       <c r="R55" t="n">
-        <v>1.88</v>
+        <v>1.83</v>
       </c>
       <c r="S55" t="n">
-        <v>-96778</v>
+        <v>-103680</v>
       </c>
       <c r="T55" t="n">
         <v>21</v>
@@ -43339,7 +42124,7 @@
         </is>
       </c>
       <c r="J56" t="n">
-        <v>62.9</v>
+        <v>62.8</v>
       </c>
       <c r="K56" t="inlineStr">
         <is>
@@ -43358,7 +42143,7 @@
         <v>49.15</v>
       </c>
       <c r="O56" t="n">
-        <v>30685.87</v>
+        <v>30685.82</v>
       </c>
       <c r="P56" t="inlineStr">
         <is>
@@ -43372,7 +42157,7 @@
         <v>3.64</v>
       </c>
       <c r="S56" t="n">
-        <v>14058</v>
+        <v>12558</v>
       </c>
       <c r="T56" t="n">
         <v>39</v>
@@ -43459,7 +42244,7 @@
         </is>
       </c>
       <c r="J57" t="n">
-        <v>52.3</v>
+        <v>52.4</v>
       </c>
       <c r="K57" t="inlineStr">
         <is>
@@ -43478,7 +42263,7 @@
         <v>50.32</v>
       </c>
       <c r="O57" t="n">
-        <v>30691.13</v>
+        <v>30691.08</v>
       </c>
       <c r="P57" t="inlineStr">
         <is>
@@ -43489,10 +42274,10 @@
         <v>30648.81</v>
       </c>
       <c r="R57" t="n">
-        <v>3.28</v>
+        <v>3.29</v>
       </c>
       <c r="S57" t="n">
-        <v>2984</v>
+        <v>1378</v>
       </c>
       <c r="T57" t="n">
         <v>39</v>
@@ -43515,7 +42300,6 @@
           <t>Round</t>
         </is>
       </c>
-      <c r="Y57" t="inlineStr"/>
       <c r="Z57" t="n">
         <v>1.1</v>
       </c>
@@ -43575,7 +42359,7 @@
         </is>
       </c>
       <c r="J58" t="n">
-        <v>67.90000000000001</v>
+        <v>67.7</v>
       </c>
       <c r="K58" t="inlineStr">
         <is>
@@ -43605,10 +42389,10 @@
         <v>4209.75</v>
       </c>
       <c r="R58" t="n">
-        <v>1.16</v>
+        <v>1.9</v>
       </c>
       <c r="S58" t="n">
-        <v>1170</v>
+        <v>1046</v>
       </c>
       <c r="T58" t="n">
         <v>29</v>
@@ -43631,9 +42415,8 @@
           <t>Round</t>
         </is>
       </c>
-      <c r="Y58" t="inlineStr"/>
       <c r="Z58" t="n">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="AA58" t="inlineStr">
         <is>
@@ -43691,7 +42474,7 @@
         </is>
       </c>
       <c r="J59" t="n">
-        <v>61.8</v>
+        <v>61.7</v>
       </c>
       <c r="K59" t="inlineStr">
         <is>
@@ -43710,7 +42493,7 @@
         <v>43.62</v>
       </c>
       <c r="O59" t="n">
-        <v>31145.65</v>
+        <v>31145.71</v>
       </c>
       <c r="P59" t="inlineStr">
         <is>
@@ -43721,10 +42504,10 @@
         <v>31105.27</v>
       </c>
       <c r="R59" t="n">
-        <v>0.95</v>
+        <v>0.93</v>
       </c>
       <c r="S59" t="n">
-        <v>20909</v>
+        <v>20711</v>
       </c>
       <c r="T59" t="n">
         <v>81</v>
@@ -43749,7 +42532,7 @@
       </c>
       <c r="Y59" t="inlineStr">
         <is>
-          <t>bearish engulfing</t>
+          <t>strong bearish close</t>
         </is>
       </c>
       <c r="Z59" t="n">
@@ -43811,7 +42594,7 @@
         </is>
       </c>
       <c r="J60" t="n">
-        <v>47.4</v>
+        <v>47.5</v>
       </c>
       <c r="K60" t="inlineStr">
         <is>
@@ -43830,7 +42613,7 @@
         <v>10.5</v>
       </c>
       <c r="O60" t="n">
-        <v>4219.79</v>
+        <v>4219.78</v>
       </c>
       <c r="P60" t="inlineStr">
         <is>
@@ -43841,10 +42624,10 @@
         <v>4214.57</v>
       </c>
       <c r="R60" t="n">
-        <v>1.14</v>
+        <v>1.17</v>
       </c>
       <c r="S60" t="n">
-        <v>3770</v>
+        <v>3500</v>
       </c>
       <c r="T60" t="n">
         <v>74</v>
@@ -43931,7 +42714,7 @@
         </is>
       </c>
       <c r="J61" t="n">
-        <v>44</v>
+        <v>44.1</v>
       </c>
       <c r="K61" t="inlineStr">
         <is>
@@ -43950,7 +42733,7 @@
         <v>10.43</v>
       </c>
       <c r="O61" t="n">
-        <v>4219.57</v>
+        <v>4219.55</v>
       </c>
       <c r="P61" t="inlineStr">
         <is>
@@ -43961,10 +42744,10 @@
         <v>4214.57</v>
       </c>
       <c r="R61" t="n">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="S61" t="n">
-        <v>4000</v>
+        <v>3714</v>
       </c>
       <c r="T61" t="n">
         <v>74</v>
@@ -44070,7 +42853,7 @@
         <v>46.65</v>
       </c>
       <c r="O62" t="n">
-        <v>31180.8</v>
+        <v>31180.84</v>
       </c>
       <c r="P62" t="inlineStr">
         <is>
@@ -44084,7 +42867,7 @@
         <v>0.78</v>
       </c>
       <c r="S62" t="n">
-        <v>49171</v>
+        <v>49059</v>
       </c>
       <c r="T62" t="n">
         <v>6</v>
@@ -44123,6 +42906,3369 @@
       <c r="AB62" t="inlineStr">
         <is>
           <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>2026-10-04</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>21:32</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>MGC</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>Short</t>
+        </is>
+      </c>
+      <c r="E63" t="n">
+        <v>-97</v>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>down</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>down</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>down</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr">
+        <is>
+          <t>up</t>
+        </is>
+      </c>
+      <c r="J63" t="n">
+        <v>53.9</v>
+      </c>
+      <c r="K63" t="inlineStr">
+        <is>
+          <t>bull</t>
+        </is>
+      </c>
+      <c r="L63" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M63" t="n">
+        <v>29.9</v>
+      </c>
+      <c r="N63" t="n">
+        <v>3.54</v>
+      </c>
+      <c r="O63" t="n">
+        <v>4178.25</v>
+      </c>
+      <c r="P63" t="inlineStr">
+        <is>
+          <t>above</t>
+        </is>
+      </c>
+      <c r="Q63" t="n">
+        <v>4184.49</v>
+      </c>
+      <c r="R63" t="n">
+        <v>0.43</v>
+      </c>
+      <c r="S63" t="n">
+        <v>874</v>
+      </c>
+      <c r="T63" t="n">
+        <v>45</v>
+      </c>
+      <c r="U63" t="inlineStr">
+        <is>
+          <t>golden</t>
+        </is>
+      </c>
+      <c r="V63" t="inlineStr">
+        <is>
+          <t>A+</t>
+        </is>
+      </c>
+      <c r="W63" t="n">
+        <v>3</v>
+      </c>
+      <c r="X63" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="Y63" t="inlineStr">
+        <is>
+          <t>strong bearish close</t>
+        </is>
+      </c>
+      <c r="Z63" t="n">
+        <v>0.88</v>
+      </c>
+      <c r="AA63" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AB63" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>2026-10-04</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>21:55</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>MGC</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>Short</t>
+        </is>
+      </c>
+      <c r="E64" t="n">
+        <v>-57</v>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>down</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>down</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>up</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr">
+        <is>
+          <t>up</t>
+        </is>
+      </c>
+      <c r="J64" t="n">
+        <v>62.6</v>
+      </c>
+      <c r="K64" t="inlineStr">
+        <is>
+          <t>bull</t>
+        </is>
+      </c>
+      <c r="L64" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M64" t="n">
+        <v>27.4</v>
+      </c>
+      <c r="N64" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="O64" t="n">
+        <v>4178.97</v>
+      </c>
+      <c r="P64" t="inlineStr">
+        <is>
+          <t>above</t>
+        </is>
+      </c>
+      <c r="Q64" t="n">
+        <v>4183.33</v>
+      </c>
+      <c r="R64" t="n">
+        <v>0.65</v>
+      </c>
+      <c r="S64" t="n">
+        <v>1018</v>
+      </c>
+      <c r="T64" t="n">
+        <v>72</v>
+      </c>
+      <c r="U64" t="inlineStr">
+        <is>
+          <t>deep</t>
+        </is>
+      </c>
+      <c r="V64" t="inlineStr">
+        <is>
+          <t>Weak</t>
+        </is>
+      </c>
+      <c r="W64" t="n">
+        <v>1</v>
+      </c>
+      <c r="X64" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="Z64" t="n">
+        <v>0.82</v>
+      </c>
+      <c r="AA64" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AB64" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>2026-10-04</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>21:58</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>MGC</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>Long</t>
+        </is>
+      </c>
+      <c r="E65" t="n">
+        <v>18</v>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>down</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>down</t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>up</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr">
+        <is>
+          <t>up</t>
+        </is>
+      </c>
+      <c r="J65" t="n">
+        <v>62.6</v>
+      </c>
+      <c r="K65" t="inlineStr">
+        <is>
+          <t>bull</t>
+        </is>
+      </c>
+      <c r="L65" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M65" t="n">
+        <v>27.4</v>
+      </c>
+      <c r="N65" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="O65" t="n">
+        <v>4178.97</v>
+      </c>
+      <c r="P65" t="inlineStr">
+        <is>
+          <t>above</t>
+        </is>
+      </c>
+      <c r="Q65" t="n">
+        <v>4183.33</v>
+      </c>
+      <c r="R65" t="n">
+        <v>0.65</v>
+      </c>
+      <c r="S65" t="n">
+        <v>1018</v>
+      </c>
+      <c r="T65" t="n">
+        <v>3</v>
+      </c>
+      <c r="U65" t="inlineStr">
+        <is>
+          <t>extended (no pullback)</t>
+        </is>
+      </c>
+      <c r="V65" t="inlineStr">
+        <is>
+          <t>No setup</t>
+        </is>
+      </c>
+      <c r="W65" t="n">
+        <v>0</v>
+      </c>
+      <c r="X65" t="inlineStr">
+        <is>
+          <t>Round</t>
+        </is>
+      </c>
+      <c r="Z65" t="n">
+        <v>0.82</v>
+      </c>
+      <c r="AA65" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AB65" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>2026-10-04</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>22:32</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>MGC</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>Long</t>
+        </is>
+      </c>
+      <c r="E66" t="n">
+        <v>-447</v>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>down</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>down</t>
+        </is>
+      </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>up</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr">
+        <is>
+          <t>up</t>
+        </is>
+      </c>
+      <c r="J66" t="n">
+        <v>46.1</v>
+      </c>
+      <c r="K66" t="inlineStr">
+        <is>
+          <t>bull</t>
+        </is>
+      </c>
+      <c r="L66" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M66" t="n">
+        <v>24.8</v>
+      </c>
+      <c r="N66" t="n">
+        <v>3.72</v>
+      </c>
+      <c r="O66" t="n">
+        <v>4180.53</v>
+      </c>
+      <c r="P66" t="inlineStr">
+        <is>
+          <t>above</t>
+        </is>
+      </c>
+      <c r="Q66" t="n">
+        <v>4184.65</v>
+      </c>
+      <c r="R66" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="S66" t="n">
+        <v>709</v>
+      </c>
+      <c r="T66" t="n">
+        <v>23</v>
+      </c>
+      <c r="U66" t="inlineStr">
+        <is>
+          <t>shallow</t>
+        </is>
+      </c>
+      <c r="V66" t="inlineStr">
+        <is>
+          <t>Weak</t>
+        </is>
+      </c>
+      <c r="W66" t="n">
+        <v>1</v>
+      </c>
+      <c r="X66" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="Y66" t="inlineStr">
+        <is>
+          <t>strong bearish close</t>
+        </is>
+      </c>
+      <c r="Z66" t="n">
+        <v>0.71</v>
+      </c>
+      <c r="AA66" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AB66" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>2026-10-04</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>22:58</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>MGC</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>Long</t>
+        </is>
+      </c>
+      <c r="E67" t="n">
+        <v>7</v>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>down</t>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>down</t>
+        </is>
+      </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>up</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr">
+        <is>
+          <t>down</t>
+        </is>
+      </c>
+      <c r="J67" t="n">
+        <v>28.3</v>
+      </c>
+      <c r="K67" t="inlineStr">
+        <is>
+          <t>bear</t>
+        </is>
+      </c>
+      <c r="L67" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M67" t="n">
+        <v>26.2</v>
+      </c>
+      <c r="N67" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="O67" t="n">
+        <v>4179.35</v>
+      </c>
+      <c r="P67" t="inlineStr">
+        <is>
+          <t>below</t>
+        </is>
+      </c>
+      <c r="Q67" t="n">
+        <v>4169.52</v>
+      </c>
+      <c r="R67" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="S67" t="n">
+        <v>-44</v>
+      </c>
+      <c r="T67" t="n">
+        <v>71</v>
+      </c>
+      <c r="U67" t="inlineStr">
+        <is>
+          <t>deep</t>
+        </is>
+      </c>
+      <c r="V67" t="inlineStr">
+        <is>
+          <t>No setup</t>
+        </is>
+      </c>
+      <c r="W67" t="n">
+        <v>0</v>
+      </c>
+      <c r="X67" t="inlineStr">
+        <is>
+          <t>Round</t>
+        </is>
+      </c>
+      <c r="Z67" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="AA67" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AB67" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>2026-10-04</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>23:03</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>MGC</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>Short</t>
+        </is>
+      </c>
+      <c r="E68" t="n">
+        <v>5</v>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>down</t>
+        </is>
+      </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>down</t>
+        </is>
+      </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>down</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr">
+        <is>
+          <t>down</t>
+        </is>
+      </c>
+      <c r="J68" t="n">
+        <v>29.1</v>
+      </c>
+      <c r="K68" t="inlineStr">
+        <is>
+          <t>bear</t>
+        </is>
+      </c>
+      <c r="L68" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M68" t="n">
+        <v>27.5</v>
+      </c>
+      <c r="N68" t="n">
+        <v>3.97</v>
+      </c>
+      <c r="O68" t="n">
+        <v>4179</v>
+      </c>
+      <c r="P68" t="inlineStr">
+        <is>
+          <t>below</t>
+        </is>
+      </c>
+      <c r="Q68" t="n">
+        <v>4169.52</v>
+      </c>
+      <c r="R68" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="S68" t="n">
+        <v>-44</v>
+      </c>
+      <c r="T68" t="n">
+        <v>0</v>
+      </c>
+      <c r="U68" t="inlineStr">
+        <is>
+          <t>extended (no pullback)</t>
+        </is>
+      </c>
+      <c r="V68" t="inlineStr">
+        <is>
+          <t>Weak</t>
+        </is>
+      </c>
+      <c r="W68" t="n">
+        <v>1</v>
+      </c>
+      <c r="X68" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="Z68" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="AA68" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AB68" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>10:09</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>MNQ</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>Long</t>
+        </is>
+      </c>
+      <c r="E69" t="n">
+        <v>10</v>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>up</t>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>up</t>
+        </is>
+      </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>up</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr">
+        <is>
+          <t>up</t>
+        </is>
+      </c>
+      <c r="J69" t="n">
+        <v>71.90000000000001</v>
+      </c>
+      <c r="K69" t="inlineStr">
+        <is>
+          <t>bull</t>
+        </is>
+      </c>
+      <c r="L69" t="inlineStr">
+        <is>
+          <t>+</t>
+        </is>
+      </c>
+      <c r="M69" t="n">
+        <v>31.9</v>
+      </c>
+      <c r="N69" t="n">
+        <v>30.51</v>
+      </c>
+      <c r="O69" t="n">
+        <v>31519.31</v>
+      </c>
+      <c r="P69" t="inlineStr">
+        <is>
+          <t>above</t>
+        </is>
+      </c>
+      <c r="Q69" t="n">
+        <v>31522.92</v>
+      </c>
+      <c r="R69" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="S69" t="n">
+        <v>21457</v>
+      </c>
+      <c r="T69" t="n">
+        <v>9</v>
+      </c>
+      <c r="U69" t="inlineStr">
+        <is>
+          <t>extended (no pullback)</t>
+        </is>
+      </c>
+      <c r="V69" t="inlineStr">
+        <is>
+          <t>Weak</t>
+        </is>
+      </c>
+      <c r="W69" t="n">
+        <v>1</v>
+      </c>
+      <c r="X69" t="inlineStr">
+        <is>
+          <t>ORH/Round</t>
+        </is>
+      </c>
+      <c r="Y69" t="inlineStr">
+        <is>
+          <t>strong bullish close</t>
+        </is>
+      </c>
+      <c r="Z69" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="AA69" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AB69" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>10:24</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>MGC</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>Short</t>
+        </is>
+      </c>
+      <c r="E70" t="n">
+        <v>-137</v>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>flat</t>
+        </is>
+      </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>up</t>
+        </is>
+      </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>down</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr">
+        <is>
+          <t>down</t>
+        </is>
+      </c>
+      <c r="J70" t="n">
+        <v>27.4</v>
+      </c>
+      <c r="K70" t="inlineStr">
+        <is>
+          <t>bear</t>
+        </is>
+      </c>
+      <c r="L70" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M70" t="n">
+        <v>35.1</v>
+      </c>
+      <c r="N70" t="n">
+        <v>5.04</v>
+      </c>
+      <c r="O70" t="n">
+        <v>4182.41</v>
+      </c>
+      <c r="P70" t="inlineStr">
+        <is>
+          <t>below</t>
+        </is>
+      </c>
+      <c r="Q70" t="n">
+        <v>4183.1</v>
+      </c>
+      <c r="R70" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="S70" t="n">
+        <v>-2763</v>
+      </c>
+      <c r="T70" t="n">
+        <v>8</v>
+      </c>
+      <c r="U70" t="inlineStr">
+        <is>
+          <t>extended (no pullback)</t>
+        </is>
+      </c>
+      <c r="V70" t="inlineStr">
+        <is>
+          <t>No setup</t>
+        </is>
+      </c>
+      <c r="W70" t="n">
+        <v>0</v>
+      </c>
+      <c r="X70" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="Z70" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="AA70" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AB70" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>12:48</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>MNQ</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>Long</t>
+        </is>
+      </c>
+      <c r="E71" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>up</t>
+        </is>
+      </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>up</t>
+        </is>
+      </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>up</t>
+        </is>
+      </c>
+      <c r="I71" t="inlineStr">
+        <is>
+          <t>up</t>
+        </is>
+      </c>
+      <c r="J71" t="n">
+        <v>43.3</v>
+      </c>
+      <c r="K71" t="inlineStr">
+        <is>
+          <t>bear</t>
+        </is>
+      </c>
+      <c r="L71" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M71" t="n">
+        <v>25.4</v>
+      </c>
+      <c r="N71" t="n">
+        <v>22.44</v>
+      </c>
+      <c r="O71" t="n">
+        <v>31544.98</v>
+      </c>
+      <c r="P71" t="inlineStr">
+        <is>
+          <t>below</t>
+        </is>
+      </c>
+      <c r="Q71" t="n">
+        <v>31523.23</v>
+      </c>
+      <c r="R71" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="S71" t="n">
+        <v>35056</v>
+      </c>
+      <c r="T71" t="n">
+        <v>49</v>
+      </c>
+      <c r="U71" t="inlineStr">
+        <is>
+          <t>golden</t>
+        </is>
+      </c>
+      <c r="V71" t="inlineStr">
+        <is>
+          <t>Good</t>
+        </is>
+      </c>
+      <c r="W71" t="n">
+        <v>2</v>
+      </c>
+      <c r="X71" t="inlineStr">
+        <is>
+          <t>ONH</t>
+        </is>
+      </c>
+      <c r="Z71" t="n">
+        <v>0.86</v>
+      </c>
+      <c r="AA71" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AB71" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>14:01</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>MNQ</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>Short</t>
+        </is>
+      </c>
+      <c r="E72" t="n">
+        <v>32.5</v>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>up</t>
+        </is>
+      </c>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>up</t>
+        </is>
+      </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>up</t>
+        </is>
+      </c>
+      <c r="I72" t="inlineStr">
+        <is>
+          <t>down</t>
+        </is>
+      </c>
+      <c r="J72" t="n">
+        <v>58.5</v>
+      </c>
+      <c r="K72" t="inlineStr">
+        <is>
+          <t>bear</t>
+        </is>
+      </c>
+      <c r="L72" t="inlineStr">
+        <is>
+          <t>+</t>
+        </is>
+      </c>
+      <c r="M72" t="n">
+        <v>25.2</v>
+      </c>
+      <c r="N72" t="n">
+        <v>20.49</v>
+      </c>
+      <c r="O72" t="n">
+        <v>31540.63</v>
+      </c>
+      <c r="P72" t="inlineStr">
+        <is>
+          <t>below</t>
+        </is>
+      </c>
+      <c r="Q72" t="n">
+        <v>31523.23</v>
+      </c>
+      <c r="R72" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="S72" t="n">
+        <v>44258</v>
+      </c>
+      <c r="T72" t="n">
+        <v>37</v>
+      </c>
+      <c r="U72" t="inlineStr">
+        <is>
+          <t>shallow</t>
+        </is>
+      </c>
+      <c r="V72" t="inlineStr">
+        <is>
+          <t>Weak</t>
+        </is>
+      </c>
+      <c r="W72" t="n">
+        <v>1</v>
+      </c>
+      <c r="X72" t="inlineStr">
+        <is>
+          <t>ONH</t>
+        </is>
+      </c>
+      <c r="Y72" t="inlineStr">
+        <is>
+          <t>bullish engulfing</t>
+        </is>
+      </c>
+      <c r="Z72" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="AA72" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AB72" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>15:05</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>MNQ</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>Short</t>
+        </is>
+      </c>
+      <c r="E73" t="n">
+        <v>52</v>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>up</t>
+        </is>
+      </c>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>up</t>
+        </is>
+      </c>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>up</t>
+        </is>
+      </c>
+      <c r="I73" t="inlineStr">
+        <is>
+          <t>down</t>
+        </is>
+      </c>
+      <c r="J73" t="n">
+        <v>39.8</v>
+      </c>
+      <c r="K73" t="inlineStr">
+        <is>
+          <t>bear</t>
+        </is>
+      </c>
+      <c r="L73" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M73" t="n">
+        <v>19.6</v>
+      </c>
+      <c r="N73" t="n">
+        <v>17.18</v>
+      </c>
+      <c r="O73" t="n">
+        <v>31539.36</v>
+      </c>
+      <c r="P73" t="inlineStr">
+        <is>
+          <t>below</t>
+        </is>
+      </c>
+      <c r="Q73" t="n">
+        <v>31523.23</v>
+      </c>
+      <c r="R73" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="S73" t="n">
+        <v>39545</v>
+      </c>
+      <c r="T73" t="n">
+        <v>38</v>
+      </c>
+      <c r="U73" t="inlineStr">
+        <is>
+          <t>golden</t>
+        </is>
+      </c>
+      <c r="V73" t="inlineStr">
+        <is>
+          <t>Good</t>
+        </is>
+      </c>
+      <c r="W73" t="n">
+        <v>2</v>
+      </c>
+      <c r="X73" t="inlineStr">
+        <is>
+          <t>ONH</t>
+        </is>
+      </c>
+      <c r="Y73" t="inlineStr">
+        <is>
+          <t>strong bearish close</t>
+        </is>
+      </c>
+      <c r="Z73" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="AA73" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AB73" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>09:45</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>MES</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>Short</t>
+        </is>
+      </c>
+      <c r="E74" t="n">
+        <v>5</v>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>flat</t>
+        </is>
+      </c>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>down</t>
+        </is>
+      </c>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>down</t>
+        </is>
+      </c>
+      <c r="I74" t="inlineStr">
+        <is>
+          <t>down</t>
+        </is>
+      </c>
+      <c r="J74" t="n">
+        <v>23.7</v>
+      </c>
+      <c r="K74" t="inlineStr">
+        <is>
+          <t>bear</t>
+        </is>
+      </c>
+      <c r="L74" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M74" t="n">
+        <v>47.3</v>
+      </c>
+      <c r="N74" t="n">
+        <v>5.32</v>
+      </c>
+      <c r="O74" t="n">
+        <v>7829.69</v>
+      </c>
+      <c r="P74" t="inlineStr">
+        <is>
+          <t>below</t>
+        </is>
+      </c>
+      <c r="Q74" t="n">
+        <v>7838.02</v>
+      </c>
+      <c r="R74" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="S74" t="n">
+        <v>-65247</v>
+      </c>
+      <c r="T74" t="n">
+        <v>14</v>
+      </c>
+      <c r="U74" t="inlineStr">
+        <is>
+          <t>extended (no pullback)</t>
+        </is>
+      </c>
+      <c r="V74" t="inlineStr">
+        <is>
+          <t>Good</t>
+        </is>
+      </c>
+      <c r="W74" t="n">
+        <v>2</v>
+      </c>
+      <c r="X74" t="inlineStr">
+        <is>
+          <t>PDL</t>
+        </is>
+      </c>
+      <c r="Y74" t="inlineStr">
+        <is>
+          <t>bearish engulfing</t>
+        </is>
+      </c>
+      <c r="Z74" t="n">
+        <v>3.19</v>
+      </c>
+      <c r="AA74" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AB74" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>10:36</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>MGC</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>Long</t>
+        </is>
+      </c>
+      <c r="E75" t="n">
+        <v>-84</v>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>down</t>
+        </is>
+      </c>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>down</t>
+        </is>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>down</t>
+        </is>
+      </c>
+      <c r="I75" t="inlineStr">
+        <is>
+          <t>up</t>
+        </is>
+      </c>
+      <c r="J75" t="n">
+        <v>60.9</v>
+      </c>
+      <c r="K75" t="inlineStr">
+        <is>
+          <t>bull</t>
+        </is>
+      </c>
+      <c r="L75" t="inlineStr">
+        <is>
+          <t>+</t>
+        </is>
+      </c>
+      <c r="M75" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="N75" t="n">
+        <v>6.72</v>
+      </c>
+      <c r="O75" t="n">
+        <v>4121.15</v>
+      </c>
+      <c r="P75" t="inlineStr">
+        <is>
+          <t>above</t>
+        </is>
+      </c>
+      <c r="Q75" t="n">
+        <v>4123.68</v>
+      </c>
+      <c r="R75" t="n">
+        <v>1</v>
+      </c>
+      <c r="S75" t="n">
+        <v>439</v>
+      </c>
+      <c r="T75" t="n">
+        <v>1</v>
+      </c>
+      <c r="U75" t="inlineStr">
+        <is>
+          <t>extended (no pullback)</t>
+        </is>
+      </c>
+      <c r="V75" t="inlineStr">
+        <is>
+          <t>No setup</t>
+        </is>
+      </c>
+      <c r="W75" t="n">
+        <v>0</v>
+      </c>
+      <c r="X75" t="inlineStr">
+        <is>
+          <t>PDL/Round</t>
+        </is>
+      </c>
+      <c r="Y75" t="inlineStr">
+        <is>
+          <t>bullish pin/hammer</t>
+        </is>
+      </c>
+      <c r="Z75" t="n">
+        <v>0.8100000000000001</v>
+      </c>
+      <c r="AA75" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AB75" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>10:55</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>MNQ</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>Short</t>
+        </is>
+      </c>
+      <c r="E76" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>flat</t>
+        </is>
+      </c>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>down</t>
+        </is>
+      </c>
+      <c r="H76" t="inlineStr">
+        <is>
+          <t>down</t>
+        </is>
+      </c>
+      <c r="I76" t="inlineStr">
+        <is>
+          <t>down</t>
+        </is>
+      </c>
+      <c r="J76" t="n">
+        <v>52.3</v>
+      </c>
+      <c r="K76" t="inlineStr">
+        <is>
+          <t>bull</t>
+        </is>
+      </c>
+      <c r="L76" t="inlineStr">
+        <is>
+          <t>+</t>
+        </is>
+      </c>
+      <c r="M76" t="n">
+        <v>20.8</v>
+      </c>
+      <c r="N76" t="n">
+        <v>36.39</v>
+      </c>
+      <c r="O76" t="n">
+        <v>31224.93</v>
+      </c>
+      <c r="P76" t="inlineStr">
+        <is>
+          <t>above</t>
+        </is>
+      </c>
+      <c r="Q76" t="n">
+        <v>31246.49</v>
+      </c>
+      <c r="R76" t="n">
+        <v>1</v>
+      </c>
+      <c r="S76" t="n">
+        <v>19154</v>
+      </c>
+      <c r="T76" t="n">
+        <v>39</v>
+      </c>
+      <c r="U76" t="inlineStr">
+        <is>
+          <t>golden</t>
+        </is>
+      </c>
+      <c r="V76" t="inlineStr">
+        <is>
+          <t>Weak</t>
+        </is>
+      </c>
+      <c r="W76" t="n">
+        <v>1</v>
+      </c>
+      <c r="X76" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="Y76" t="inlineStr">
+        <is>
+          <t>bullish engulfing</t>
+        </is>
+      </c>
+      <c r="Z76" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="AA76" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AB76" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>11:05</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>MGC</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>Short</t>
+        </is>
+      </c>
+      <c r="E77" t="n">
+        <v>4</v>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>down</t>
+        </is>
+      </c>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>down</t>
+        </is>
+      </c>
+      <c r="H77" t="inlineStr">
+        <is>
+          <t>down</t>
+        </is>
+      </c>
+      <c r="I77" t="inlineStr">
+        <is>
+          <t>up</t>
+        </is>
+      </c>
+      <c r="J77" t="n">
+        <v>56.4</v>
+      </c>
+      <c r="K77" t="inlineStr">
+        <is>
+          <t>bull</t>
+        </is>
+      </c>
+      <c r="L77" t="inlineStr">
+        <is>
+          <t>+</t>
+        </is>
+      </c>
+      <c r="M77" t="n">
+        <v>20.5</v>
+      </c>
+      <c r="N77" t="n">
+        <v>6.28</v>
+      </c>
+      <c r="O77" t="n">
+        <v>4123.02</v>
+      </c>
+      <c r="P77" t="inlineStr">
+        <is>
+          <t>above</t>
+        </is>
+      </c>
+      <c r="Q77" t="n">
+        <v>4123.8</v>
+      </c>
+      <c r="R77" t="n">
+        <v>0.51</v>
+      </c>
+      <c r="S77" t="n">
+        <v>-1443</v>
+      </c>
+      <c r="T77" t="n">
+        <v>62</v>
+      </c>
+      <c r="U77" t="inlineStr">
+        <is>
+          <t>golden</t>
+        </is>
+      </c>
+      <c r="V77" t="inlineStr">
+        <is>
+          <t>Good</t>
+        </is>
+      </c>
+      <c r="W77" t="n">
+        <v>2</v>
+      </c>
+      <c r="X77" t="inlineStr">
+        <is>
+          <t>PDL/ORH/Round</t>
+        </is>
+      </c>
+      <c r="Y77" t="inlineStr">
+        <is>
+          <t>strong bullish close</t>
+        </is>
+      </c>
+      <c r="Z77" t="n">
+        <v>0.52</v>
+      </c>
+      <c r="AA77" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AB77" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:H8"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="12" customWidth="1" min="1" max="1"/>
+    <col width="10" customWidth="1" min="2" max="2"/>
+    <col width="9" customWidth="1" min="3" max="3"/>
+    <col width="8" customWidth="1" min="4" max="4"/>
+    <col width="34" customWidth="1" min="5" max="5"/>
+    <col width="10" customWidth="1" min="6" max="6"/>
+    <col width="10" customWidth="1" min="7" max="7"/>
+    <col width="10" customWidth="1" min="8" max="8"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="24" t="inlineStr">
+        <is>
+          <t>Date</t>
+        </is>
+      </c>
+      <c r="B1" s="24" t="inlineStr">
+        <is>
+          <t>Time (ET)</t>
+        </is>
+      </c>
+      <c r="C1" s="24" t="inlineStr">
+        <is>
+          <t>Currency</t>
+        </is>
+      </c>
+      <c r="D1" s="24" t="inlineStr">
+        <is>
+          <t>Impact</t>
+        </is>
+      </c>
+      <c r="E1" s="24" t="inlineStr">
+        <is>
+          <t>Event</t>
+        </is>
+      </c>
+      <c r="F1" s="24" t="inlineStr">
+        <is>
+          <t>Actual</t>
+        </is>
+      </c>
+      <c r="G1" s="24" t="inlineStr">
+        <is>
+          <t>Forecast</t>
+        </is>
+      </c>
+      <c r="H1" s="24" t="inlineStr">
+        <is>
+          <t>Previous</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>08:15</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>Payrolls</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>90K</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>73K</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>36K</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>08:30</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>PCE</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>0.2%</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>0.3%</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>0.1%</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>08:30</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>GDP</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>2.2%</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>1.5%</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>2.1%</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>10:00</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>ISM</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>52.7</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>52.0</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>51.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>2026-10-03</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>08:30</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>Payrolls</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>-17.0K</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>44.0K</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>2026-10-03</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>08:30</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>Unemployment Rate</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>7.6%</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>7.7%</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>10:00</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>ISM</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>56.5</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>61.7</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E86"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="30" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="25" t="inlineStr">
+        <is>
+          <t>Overview</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Generated</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>2026-10-07 15:54</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Date range</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>2026-09-23 → 2026-10-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Trades</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Win rate</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>61.8%</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Total P&amp;L</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>-1178.25</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Profit factor</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>0.71</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Expectancy / trade</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>-15.5</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Avg win</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>60.82</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Avg loss</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>-139.21</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Avg RR targeted</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>1.3</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Avg RR realized</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>0.19</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Max drawdown</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>-1697.5</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Max win streak</t>
+        </is>
+      </c>
+      <c r="B14" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Max loss streak</t>
+        </is>
+      </c>
+      <c r="B15" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="25" t="inlineStr">
+        <is>
+          <t>By Setup</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="24" t="inlineStr">
+        <is>
+          <t>Setup</t>
+        </is>
+      </c>
+      <c r="B18" s="24" t="inlineStr">
+        <is>
+          <t>Trades</t>
+        </is>
+      </c>
+      <c r="C18" s="24" t="inlineStr">
+        <is>
+          <t>Win %</t>
+        </is>
+      </c>
+      <c r="D18" s="24" t="inlineStr">
+        <is>
+          <t>Total P&amp;L</t>
+        </is>
+      </c>
+      <c r="E18" s="24" t="inlineStr">
+        <is>
+          <t>Expectancy</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Break and Retest</t>
+        </is>
+      </c>
+      <c r="B19" t="n">
+        <v>76</v>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>62%</t>
+        </is>
+      </c>
+      <c r="D19" t="n">
+        <v>-1178.25</v>
+      </c>
+      <c r="E19" t="n">
+        <v>-15.5</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="25" t="inlineStr">
+        <is>
+          <t>By Instrument</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="24" t="inlineStr">
+        <is>
+          <t>Instrument</t>
+        </is>
+      </c>
+      <c r="B22" s="24" t="inlineStr">
+        <is>
+          <t>Trades</t>
+        </is>
+      </c>
+      <c r="C22" s="24" t="inlineStr">
+        <is>
+          <t>Win %</t>
+        </is>
+      </c>
+      <c r="D22" s="24" t="inlineStr">
+        <is>
+          <t>Total P&amp;L</t>
+        </is>
+      </c>
+      <c r="E22" s="24" t="inlineStr">
+        <is>
+          <t>Expectancy</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>MNQ</t>
+        </is>
+      </c>
+      <c r="B23" t="n">
+        <v>30</v>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>70%</t>
+        </is>
+      </c>
+      <c r="D23" t="n">
+        <v>935.5</v>
+      </c>
+      <c r="E23" t="n">
+        <v>31.18</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>MYM</t>
+        </is>
+      </c>
+      <c r="B24" t="n">
+        <v>11</v>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>45%</t>
+        </is>
+      </c>
+      <c r="D24" t="n">
+        <v>-104</v>
+      </c>
+      <c r="E24" t="n">
+        <v>-9.449999999999999</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>MES</t>
+        </is>
+      </c>
+      <c r="B25" t="n">
+        <v>12</v>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>58%</t>
+        </is>
+      </c>
+      <c r="D25" t="n">
+        <v>-178.75</v>
+      </c>
+      <c r="E25" t="n">
+        <v>-14.9</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>MGC</t>
+        </is>
+      </c>
+      <c r="B26" t="n">
+        <v>23</v>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>61%</t>
+        </is>
+      </c>
+      <c r="D26" t="n">
+        <v>-1831</v>
+      </c>
+      <c r="E26" t="n">
+        <v>-79.61</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="25" t="inlineStr">
+        <is>
+          <t>By Direction</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="24" t="inlineStr">
+        <is>
+          <t>Direction</t>
+        </is>
+      </c>
+      <c r="B29" s="24" t="inlineStr">
+        <is>
+          <t>Trades</t>
+        </is>
+      </c>
+      <c r="C29" s="24" t="inlineStr">
+        <is>
+          <t>Win %</t>
+        </is>
+      </c>
+      <c r="D29" s="24" t="inlineStr">
+        <is>
+          <t>Total P&amp;L</t>
+        </is>
+      </c>
+      <c r="E29" s="24" t="inlineStr">
+        <is>
+          <t>Expectancy</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>Short</t>
+        </is>
+      </c>
+      <c r="B30" t="n">
+        <v>43</v>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>63%</t>
+        </is>
+      </c>
+      <c r="D30" t="n">
+        <v>565.5</v>
+      </c>
+      <c r="E30" t="n">
+        <v>13.15</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>Long</t>
+        </is>
+      </c>
+      <c r="B31" t="n">
+        <v>33</v>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>61%</t>
+        </is>
+      </c>
+      <c r="D31" t="n">
+        <v>-1743.75</v>
+      </c>
+      <c r="E31" t="n">
+        <v>-52.84</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="25" t="inlineStr">
+        <is>
+          <t>By Hour</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="24" t="inlineStr">
+        <is>
+          <t>Hour</t>
+        </is>
+      </c>
+      <c r="B34" s="24" t="inlineStr">
+        <is>
+          <t>Trades</t>
+        </is>
+      </c>
+      <c r="C34" s="24" t="inlineStr">
+        <is>
+          <t>Win %</t>
+        </is>
+      </c>
+      <c r="D34" s="24" t="inlineStr">
+        <is>
+          <t>Total P&amp;L</t>
+        </is>
+      </c>
+      <c r="E34" s="24" t="inlineStr">
+        <is>
+          <t>Expectancy</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>08:00</t>
+        </is>
+      </c>
+      <c r="B35" t="n">
+        <v>1</v>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="D35" t="n">
+        <v>14</v>
+      </c>
+      <c r="E35" t="n">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>09:00</t>
+        </is>
+      </c>
+      <c r="B36" t="n">
+        <v>10</v>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>50%</t>
+        </is>
+      </c>
+      <c r="D36" t="n">
+        <v>-6</v>
+      </c>
+      <c r="E36" t="n">
+        <v>-0.6</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>10:00</t>
+        </is>
+      </c>
+      <c r="B37" t="n">
+        <v>32</v>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>53%</t>
+        </is>
+      </c>
+      <c r="D37" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="E37" t="n">
+        <v>0.08</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
+      <c r="B38" t="n">
+        <v>11</v>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>73%</t>
+        </is>
+      </c>
+      <c r="D38" t="n">
+        <v>286</v>
+      </c>
+      <c r="E38" t="n">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>12:00</t>
+        </is>
+      </c>
+      <c r="B39" t="n">
+        <v>1</v>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="D39" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="E39" t="n">
+        <v>11.5</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>13:00</t>
+        </is>
+      </c>
+      <c r="B40" t="n">
+        <v>7</v>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>71%</t>
+        </is>
+      </c>
+      <c r="D40" t="n">
+        <v>158.5</v>
+      </c>
+      <c r="E40" t="n">
+        <v>22.64</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>14:00</t>
+        </is>
+      </c>
+      <c r="B41" t="n">
+        <v>4</v>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="D41" t="n">
+        <v>64.25</v>
+      </c>
+      <c r="E41" t="n">
+        <v>16.06</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>15:00</t>
+        </is>
+      </c>
+      <c r="B42" t="n">
+        <v>1</v>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="D42" t="n">
+        <v>52</v>
+      </c>
+      <c r="E42" t="n">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>21:00</t>
+        </is>
+      </c>
+      <c r="B43" t="n">
+        <v>3</v>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>33%</t>
+        </is>
+      </c>
+      <c r="D43" t="n">
+        <v>-136</v>
+      </c>
+      <c r="E43" t="n">
+        <v>-45.33</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>22:00</t>
+        </is>
+      </c>
+      <c r="B44" t="n">
+        <v>3</v>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>67%</t>
+        </is>
+      </c>
+      <c r="D44" t="n">
+        <v>-326</v>
+      </c>
+      <c r="E44" t="n">
+        <v>-108.67</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>23:00</t>
+        </is>
+      </c>
+      <c r="B45" t="n">
+        <v>3</v>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>67%</t>
+        </is>
+      </c>
+      <c r="D45" t="n">
+        <v>-1299</v>
+      </c>
+      <c r="E45" t="n">
+        <v>-433</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="25" t="inlineStr">
+        <is>
+          <t>By Day of Week</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="24" t="inlineStr">
+        <is>
+          <t>Day</t>
+        </is>
+      </c>
+      <c r="B48" s="24" t="inlineStr">
+        <is>
+          <t>Trades</t>
+        </is>
+      </c>
+      <c r="C48" s="24" t="inlineStr">
+        <is>
+          <t>Win %</t>
+        </is>
+      </c>
+      <c r="D48" s="24" t="inlineStr">
+        <is>
+          <t>Total P&amp;L</t>
+        </is>
+      </c>
+      <c r="E48" s="24" t="inlineStr">
+        <is>
+          <t>Expectancy</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>Thu</t>
+        </is>
+      </c>
+      <c r="B49" t="n">
+        <v>23</v>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>65%</t>
+        </is>
+      </c>
+      <c r="D49" t="n">
+        <v>622.25</v>
+      </c>
+      <c r="E49" t="n">
+        <v>27.05</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>Wed</t>
+        </is>
+      </c>
+      <c r="B50" t="n">
+        <v>16</v>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>81%</t>
+        </is>
+      </c>
+      <c r="D50" t="n">
+        <v>336.5</v>
+      </c>
+      <c r="E50" t="n">
+        <v>21.03</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>Mon</t>
+        </is>
+      </c>
+      <c r="B51" t="n">
+        <v>1</v>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="D51" t="n">
+        <v>5</v>
+      </c>
+      <c r="E51" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>Fri</t>
+        </is>
+      </c>
+      <c r="B52" t="n">
+        <v>12</v>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>42%</t>
+        </is>
+      </c>
+      <c r="D52" t="n">
+        <v>-136</v>
+      </c>
+      <c r="E52" t="n">
+        <v>-11.33</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>Tue</t>
+        </is>
+      </c>
+      <c r="B53" t="n">
+        <v>16</v>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>56%</t>
+        </is>
+      </c>
+      <c r="D53" t="n">
+        <v>-240</v>
+      </c>
+      <c r="E53" t="n">
+        <v>-15</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>Sun</t>
+        </is>
+      </c>
+      <c r="B54" t="n">
+        <v>8</v>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>50%</t>
+        </is>
+      </c>
+      <c r="D54" t="n">
+        <v>-1766</v>
+      </c>
+      <c r="E54" t="n">
+        <v>-220.75</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="25" t="inlineStr">
+        <is>
+          <t>Behavior Flags</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>Overtrading</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>9 trades on 2026-09-23 (&gt; 6)</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>Overtrading</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>11 trades on 2026-09-24 (&gt; 6)</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>Overtrading</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>7 trades on 2026-09-25 (&gt; 6)</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>Overtrading</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>11 trades on 2026-09-29 (&gt; 6)</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>Overtrading</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>12 trades on 2026-10-01 (&gt; 6)</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>Possible revenge trade</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>MGC Long at 09/23 10:32 — 11 min after a loss, size 3</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>Possible revenge trade</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>MYM Long at 09/24 10:01 — 10 min after a loss, size 2</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>Possible revenge trade</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>MYM Short at 09/24 10:32 — 2 min after a loss, size 4</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>Possible revenge trade</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>MYM Long at 09/25 09:56 — 9 min after a loss, size 4</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>Possible revenge trade</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>MNQ Long at 09/25 10:40 — 8 min after a loss, size 3</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>Possible revenge trade</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>MNQ Short at 09/25 10:50 — 10 min after a loss, size 3</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>Possible revenge trade</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>MNQ Short at 09/25 10:50 — 0 min after a loss, size 3</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>Possible revenge trade</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>MYM Short at 09/29 10:00 — 13 min after a loss, size 2</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>Possible revenge trade</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>MES Long at 09/29 10:18 — 12 min after a loss, size 3</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>Possible revenge trade</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>MYM Short at 09/29 13:48 — 4 min after a loss, size 5</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>Possible revenge trade</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>MNQ Short at 10/01 10:06 — 15 min after a loss, size 2</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>Possible revenge trade</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>MNQ Short at 10/01 10:06 — 0 min after a loss, size 2</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>Possible revenge trade</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>MNQ Short at 10/01 10:10 — 4 min after a loss, size 2</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>Possible revenge trade</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>MNQ Long at 10/02 10:29 — 7 min after a loss, size 3</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>Possible revenge trade</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>MGC Long at 10/04 21:58 — 3 min after a loss, size 3</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>Winner cut short</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>MNQ 09/23 11:06 took 0.24R of 0.74R target</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>Winner cut short</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>MNQ 09/30 09:40 took 0.47R of 1.91R target</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>Negative-edge setup</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>Break and Retest: 76 trades, 62% win, $-1178 total</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>Negative-edge instrument</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>MYM: 11 trades, 45% win, $-104 total</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>Negative-edge instrument</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>MES: 12 trades, 58% win, $-179 total</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>Negative-edge instrument</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>MGC: 23 trades, 61% win, $-1831 total</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>Negative-edge hour</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>09:00: 10 trades, 50% win, $-6 total</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>Negative-edge hour</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>21:00: 3 trades, 33% win, $-136 total</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>Negative-edge hour</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>22:00: 3 trades, 67% win, $-326 total</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>Negative-edge hour</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>23:00: 3 trades, 67% win, $-1299 total</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:A3"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="120" customWidth="1" min="1" max="1"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="25" t="inlineStr">
+        <is>
+          <t>Claude AI Coaching</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="14" t="inlineStr">
+        <is>
+          <t>[AI disabled with --no-ai]</t>
         </is>
       </c>
     </row>
